--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_Lu 2006.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_Lu 2006.xlsx
@@ -1730,10 +1730,10 @@
         <v>15.81</v>
       </c>
       <c r="F13" t="n">
-        <v>20.655</v>
+        <v>20.65</v>
       </c>
       <c r="G13" t="n">
-        <v>8.32</v>
+        <v>8.31</v>
       </c>
       <c r="H13" t="n">
         <v>12.6</v>
@@ -1745,25 +1745,25 @@
         <v>19.03</v>
       </c>
       <c r="K13" t="n">
-        <v>11.372</v>
+        <v>11.37</v>
       </c>
       <c r="L13" t="n">
-        <v>16.779</v>
+        <v>16.78</v>
       </c>
       <c r="M13" t="n">
-        <v>11.744</v>
+        <v>11.74</v>
       </c>
       <c r="N13" t="n">
-        <v>16.454</v>
+        <v>16.45</v>
       </c>
       <c r="O13" t="n">
-        <v>14.075</v>
+        <v>14.07</v>
       </c>
       <c r="P13" t="n">
-        <v>14.099</v>
+        <v>14.09</v>
       </c>
       <c r="Q13" t="n">
-        <v>14.087</v>
+        <v>14.08</v>
       </c>
     </row>
     <row r="14">
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5.65</v>
+        <v>5.66</v>
       </c>
       <c r="D14" t="n">
-        <v>10.575</v>
+        <v>10.57</v>
       </c>
       <c r="E14" t="n">
-        <v>14.545</v>
+        <v>14.55</v>
       </c>
       <c r="F14" t="n">
-        <v>20.31</v>
+        <v>20.3</v>
       </c>
       <c r="G14" t="n">
-        <v>7.15</v>
+        <v>7.14</v>
       </c>
       <c r="H14" t="n">
-        <v>10.575</v>
+        <v>10.57</v>
       </c>
       <c r="I14" t="n">
-        <v>14.545</v>
+        <v>14.55</v>
       </c>
       <c r="J14" t="n">
         <v>18.36</v>
@@ -1803,22 +1803,22 @@
         <v>9.59</v>
       </c>
       <c r="L14" t="n">
-        <v>15.698</v>
+        <v>15.7</v>
       </c>
       <c r="M14" t="n">
-        <v>9.890000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>15.308</v>
+        <v>15.31</v>
       </c>
       <c r="O14" t="n">
-        <v>12.644</v>
+        <v>12.64</v>
       </c>
       <c r="P14" t="n">
-        <v>12.599</v>
+        <v>12.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.622</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="15">
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.26</v>
+        <v>5.25</v>
       </c>
       <c r="D15" t="n">
         <v>10.35</v>
@@ -1840,10 +1840,10 @@
         <v>14.66</v>
       </c>
       <c r="F15" t="n">
-        <v>20.655</v>
+        <v>20.66</v>
       </c>
       <c r="G15" t="n">
-        <v>6.835</v>
+        <v>6.83</v>
       </c>
       <c r="H15" t="n">
         <v>10.35</v>
@@ -1855,25 +1855,25 @@
         <v>18.63</v>
       </c>
       <c r="K15" t="n">
-        <v>9.332000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="L15" t="n">
-        <v>15.859</v>
+        <v>15.86</v>
       </c>
       <c r="M15" t="n">
-        <v>9.647</v>
+        <v>9.65</v>
       </c>
       <c r="N15" t="n">
-        <v>15.454</v>
+        <v>15.45</v>
       </c>
       <c r="O15" t="n">
-        <v>12.596</v>
+        <v>12.59</v>
       </c>
       <c r="P15" t="n">
         <v>12.55</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.573</v>
+        <v>12.57</v>
       </c>
     </row>
     <row r="16">
@@ -1889,22 +1889,22 @@
         <v>4.45</v>
       </c>
       <c r="D16" t="n">
-        <v>8.324999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="E16" t="n">
-        <v>13.395</v>
+        <v>13.39</v>
       </c>
       <c r="F16" t="n">
-        <v>20.31</v>
+        <v>20.32</v>
       </c>
       <c r="G16" t="n">
-        <v>5.665</v>
+        <v>5.66</v>
       </c>
       <c r="H16" t="n">
-        <v>8.324999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="I16" t="n">
-        <v>13.395</v>
+        <v>13.39</v>
       </c>
       <c r="J16" t="n">
         <v>17.96</v>
@@ -1913,22 +1913,22 @@
         <v>7.55</v>
       </c>
       <c r="L16" t="n">
-        <v>14.778</v>
+        <v>14.78</v>
       </c>
       <c r="M16" t="n">
-        <v>7.793</v>
+        <v>7.79</v>
       </c>
       <c r="N16" t="n">
-        <v>14.308</v>
+        <v>14.3</v>
       </c>
       <c r="O16" t="n">
-        <v>11.164</v>
+        <v>11.16</v>
       </c>
       <c r="P16" t="n">
-        <v>11.05</v>
+        <v>11.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>11.107</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="17">
@@ -1944,22 +1944,22 @@
         <v>4.45</v>
       </c>
       <c r="D17" t="n">
-        <v>8.324999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="E17" t="n">
-        <v>13.395</v>
+        <v>13.39</v>
       </c>
       <c r="F17" t="n">
-        <v>20.31</v>
+        <v>20.32</v>
       </c>
       <c r="G17" t="n">
-        <v>5.665</v>
+        <v>5.66</v>
       </c>
       <c r="H17" t="n">
-        <v>8.324999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="I17" t="n">
-        <v>13.395</v>
+        <v>13.39</v>
       </c>
       <c r="J17" t="n">
         <v>17.96</v>
@@ -1968,22 +1968,22 @@
         <v>7.55</v>
       </c>
       <c r="L17" t="n">
-        <v>14.778</v>
+        <v>14.78</v>
       </c>
       <c r="M17" t="n">
-        <v>7.793</v>
+        <v>7.79</v>
       </c>
       <c r="N17" t="n">
-        <v>14.308</v>
+        <v>14.3</v>
       </c>
       <c r="O17" t="n">
-        <v>11.164</v>
+        <v>11.16</v>
       </c>
       <c r="P17" t="n">
-        <v>11.05</v>
+        <v>11.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.107</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="18">
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4.495</v>
+        <v>4.5</v>
       </c>
       <c r="D18" t="n">
         <v>9.09</v>
@@ -2008,7 +2008,7 @@
         <v>17.34</v>
       </c>
       <c r="G18" t="n">
-        <v>5.635</v>
+        <v>5.63</v>
       </c>
       <c r="H18" t="n">
         <v>9.09</v>
@@ -2020,25 +2020,25 @@
         <v>15.83</v>
       </c>
       <c r="K18" t="n">
-        <v>8.170999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="L18" t="n">
-        <v>13.652</v>
+        <v>13.65</v>
       </c>
       <c r="M18" t="n">
-        <v>8.398999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="N18" t="n">
         <v>13.35</v>
       </c>
       <c r="O18" t="n">
-        <v>10.912</v>
+        <v>10.91</v>
       </c>
       <c r="P18" t="n">
-        <v>10.874</v>
+        <v>10.88</v>
       </c>
       <c r="Q18" t="n">
-        <v>10.893</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="19">
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4.495</v>
+        <v>4.5</v>
       </c>
       <c r="D19" t="n">
         <v>9.09</v>
@@ -2063,7 +2063,7 @@
         <v>17.34</v>
       </c>
       <c r="G19" t="n">
-        <v>5.635</v>
+        <v>5.63</v>
       </c>
       <c r="H19" t="n">
         <v>9.09</v>
@@ -2075,25 +2075,25 @@
         <v>15.83</v>
       </c>
       <c r="K19" t="n">
-        <v>8.170999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="L19" t="n">
-        <v>13.652</v>
+        <v>13.65</v>
       </c>
       <c r="M19" t="n">
-        <v>8.398999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="N19" t="n">
         <v>13.35</v>
       </c>
       <c r="O19" t="n">
-        <v>10.912</v>
+        <v>10.91</v>
       </c>
       <c r="P19" t="n">
-        <v>10.874</v>
+        <v>10.88</v>
       </c>
       <c r="Q19" t="n">
-        <v>10.893</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="20">
@@ -2106,46 +2106,46 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4.015</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>7.425</v>
+        <v>7.43</v>
       </c>
       <c r="E20" t="n">
-        <v>12.705</v>
+        <v>12.71</v>
       </c>
       <c r="F20" t="n">
-        <v>19.965</v>
+        <v>19.96</v>
       </c>
       <c r="G20" t="n">
         <v>5.08</v>
       </c>
       <c r="H20" t="n">
-        <v>7.425</v>
+        <v>7.43</v>
       </c>
       <c r="I20" t="n">
-        <v>12.705</v>
+        <v>12.71</v>
       </c>
       <c r="J20" t="n">
         <v>17.49</v>
       </c>
       <c r="K20" t="n">
-        <v>6.743</v>
+        <v>6.74</v>
       </c>
       <c r="L20" t="n">
-        <v>14.157</v>
+        <v>14.16</v>
       </c>
       <c r="M20" t="n">
-        <v>6.956</v>
+        <v>6.96</v>
       </c>
       <c r="N20" t="n">
-        <v>13.662</v>
+        <v>13.67</v>
       </c>
       <c r="O20" t="n">
         <v>10.45</v>
       </c>
       <c r="P20" t="n">
-        <v>10.309</v>
+        <v>10.31</v>
       </c>
       <c r="Q20" t="n">
         <v>10.38</v>
@@ -2161,49 +2161,49 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.195</v>
+        <v>2.2</v>
       </c>
       <c r="D21" t="n">
-        <v>6.015</v>
+        <v>6.02</v>
       </c>
       <c r="E21" t="n">
-        <v>10.755</v>
+        <v>10.75</v>
       </c>
       <c r="F21" t="n">
-        <v>16.215</v>
+        <v>16.21</v>
       </c>
       <c r="G21" t="n">
-        <v>3.125</v>
+        <v>3.12</v>
       </c>
       <c r="H21" t="n">
-        <v>6.015</v>
+        <v>6.02</v>
       </c>
       <c r="I21" t="n">
-        <v>10.755</v>
+        <v>10.75</v>
       </c>
       <c r="J21" t="n">
         <v>14.43</v>
       </c>
       <c r="K21" t="n">
-        <v>5.251</v>
+        <v>5.26</v>
       </c>
       <c r="L21" t="n">
-        <v>11.847</v>
+        <v>11.84</v>
       </c>
       <c r="M21" t="n">
-        <v>5.437</v>
+        <v>5.44</v>
       </c>
       <c r="N21" t="n">
         <v>11.49</v>
       </c>
       <c r="O21" t="n">
-        <v>8.548999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>8.462999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.506</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="22">
@@ -2216,49 +2216,49 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.155</v>
+        <v>1.16</v>
       </c>
       <c r="D22" t="n">
-        <v>4.455</v>
+        <v>4.46</v>
       </c>
       <c r="E22" t="n">
-        <v>9.074999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="F22" t="n">
-        <v>14.025</v>
+        <v>14.03</v>
       </c>
       <c r="G22" t="n">
-        <v>1.819</v>
+        <v>1.81</v>
       </c>
       <c r="H22" t="n">
-        <v>4.455</v>
+        <v>4.46</v>
       </c>
       <c r="I22" t="n">
-        <v>9.074999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="J22" t="n">
         <v>12.43</v>
       </c>
       <c r="K22" t="n">
-        <v>3.795</v>
+        <v>3.8</v>
       </c>
       <c r="L22" t="n">
-        <v>10.065</v>
+        <v>10.06</v>
       </c>
       <c r="M22" t="n">
-        <v>3.928</v>
+        <v>3.93</v>
       </c>
       <c r="N22" t="n">
-        <v>9.746</v>
+        <v>9.74</v>
       </c>
       <c r="O22" t="n">
         <v>6.93</v>
       </c>
       <c r="P22" t="n">
-        <v>6.837</v>
+        <v>6.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.883</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="25">
@@ -2342,49 +2342,49 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7.3</v>
+        <v>7.29</v>
       </c>
       <c r="D28" t="n">
-        <v>13.325</v>
+        <v>13.32</v>
       </c>
       <c r="E28" t="n">
-        <v>18.395</v>
+        <v>18.39</v>
       </c>
       <c r="F28" t="n">
-        <v>25.31</v>
+        <v>25.32</v>
       </c>
       <c r="G28" t="n">
-        <v>9.115</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>13.325</v>
+        <v>13.32</v>
       </c>
       <c r="I28" t="n">
-        <v>18.395</v>
+        <v>18.39</v>
       </c>
       <c r="J28" t="n">
         <v>22.96</v>
       </c>
       <c r="K28" t="n">
-        <v>12.12</v>
+        <v>12.11</v>
       </c>
       <c r="L28" t="n">
-        <v>19.778</v>
+        <v>19.78</v>
       </c>
       <c r="M28" t="n">
-        <v>12.483</v>
+        <v>12.48</v>
       </c>
       <c r="N28" t="n">
-        <v>19.308</v>
+        <v>19.3</v>
       </c>
       <c r="O28" t="n">
-        <v>15.949</v>
+        <v>15.95</v>
       </c>
       <c r="P28" t="n">
-        <v>15.896</v>
+        <v>15.89</v>
       </c>
       <c r="Q28" t="n">
-        <v>15.922</v>
+        <v>15.92</v>
       </c>
     </row>
     <row r="29">
@@ -2397,49 +2397,49 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7.3</v>
+        <v>7.29</v>
       </c>
       <c r="D29" t="n">
-        <v>13.325</v>
+        <v>13.32</v>
       </c>
       <c r="E29" t="n">
-        <v>18.395</v>
+        <v>18.39</v>
       </c>
       <c r="F29" t="n">
-        <v>25.31</v>
+        <v>25.32</v>
       </c>
       <c r="G29" t="n">
-        <v>9.115</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>13.325</v>
+        <v>13.32</v>
       </c>
       <c r="I29" t="n">
-        <v>18.395</v>
+        <v>18.39</v>
       </c>
       <c r="J29" t="n">
         <v>22.96</v>
       </c>
       <c r="K29" t="n">
-        <v>12.12</v>
+        <v>12.11</v>
       </c>
       <c r="L29" t="n">
-        <v>19.778</v>
+        <v>19.78</v>
       </c>
       <c r="M29" t="n">
-        <v>12.483</v>
+        <v>12.48</v>
       </c>
       <c r="N29" t="n">
-        <v>19.308</v>
+        <v>19.3</v>
       </c>
       <c r="O29" t="n">
-        <v>15.949</v>
+        <v>15.95</v>
       </c>
       <c r="P29" t="n">
-        <v>15.896</v>
+        <v>15.89</v>
       </c>
       <c r="Q29" t="n">
-        <v>15.922</v>
+        <v>15.92</v>
       </c>
     </row>
     <row r="30">
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6.145</v>
+        <v>6.14</v>
       </c>
       <c r="D30" t="n">
         <v>11.84</v>
@@ -2476,25 +2476,25 @@
         <v>20.43</v>
       </c>
       <c r="K30" t="n">
-        <v>10.701</v>
+        <v>10.7</v>
       </c>
       <c r="L30" t="n">
-        <v>17.732</v>
+        <v>17.73</v>
       </c>
       <c r="M30" t="n">
-        <v>10.992</v>
+        <v>10.99</v>
       </c>
       <c r="N30" t="n">
         <v>17.35</v>
       </c>
       <c r="O30" t="n">
-        <v>14.216</v>
+        <v>14.21</v>
       </c>
       <c r="P30" t="n">
-        <v>14.171</v>
+        <v>14.17</v>
       </c>
       <c r="Q30" t="n">
-        <v>14.194</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="31">
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6.145</v>
+        <v>6.14</v>
       </c>
       <c r="D31" t="n">
         <v>11.84</v>
@@ -2531,25 +2531,25 @@
         <v>20.43</v>
       </c>
       <c r="K31" t="n">
-        <v>10.701</v>
+        <v>10.7</v>
       </c>
       <c r="L31" t="n">
-        <v>17.732</v>
+        <v>17.73</v>
       </c>
       <c r="M31" t="n">
-        <v>10.992</v>
+        <v>10.99</v>
       </c>
       <c r="N31" t="n">
         <v>17.35</v>
       </c>
       <c r="O31" t="n">
-        <v>14.216</v>
+        <v>14.21</v>
       </c>
       <c r="P31" t="n">
-        <v>14.171</v>
+        <v>14.17</v>
       </c>
       <c r="Q31" t="n">
-        <v>14.194</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="32">
@@ -2562,7 +2562,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6.145</v>
+        <v>6.14</v>
       </c>
       <c r="D32" t="n">
         <v>11.84</v>
@@ -2586,25 +2586,25 @@
         <v>20.43</v>
       </c>
       <c r="K32" t="n">
-        <v>10.701</v>
+        <v>10.7</v>
       </c>
       <c r="L32" t="n">
-        <v>17.732</v>
+        <v>17.73</v>
       </c>
       <c r="M32" t="n">
-        <v>10.992</v>
+        <v>10.99</v>
       </c>
       <c r="N32" t="n">
         <v>17.35</v>
       </c>
       <c r="O32" t="n">
-        <v>14.216</v>
+        <v>14.21</v>
       </c>
       <c r="P32" t="n">
-        <v>14.171</v>
+        <v>14.17</v>
       </c>
       <c r="Q32" t="n">
-        <v>14.194</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="33">
@@ -2617,49 +2617,49 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5.045</v>
+        <v>5.04</v>
       </c>
       <c r="D33" t="n">
-        <v>11.015</v>
+        <v>11.01</v>
       </c>
       <c r="E33" t="n">
-        <v>15.755</v>
+        <v>15.75</v>
       </c>
       <c r="F33" t="n">
-        <v>21.215</v>
+        <v>21.21</v>
       </c>
       <c r="G33" t="n">
-        <v>6.575</v>
+        <v>6.57</v>
       </c>
       <c r="H33" t="n">
-        <v>11.015</v>
+        <v>11.01</v>
       </c>
       <c r="I33" t="n">
-        <v>15.755</v>
+        <v>15.75</v>
       </c>
       <c r="J33" t="n">
         <v>19.43</v>
       </c>
       <c r="K33" t="n">
-        <v>9.821</v>
+        <v>9.82</v>
       </c>
       <c r="L33" t="n">
-        <v>16.847</v>
+        <v>16.84</v>
       </c>
       <c r="M33" t="n">
-        <v>10.127</v>
+        <v>10.12</v>
       </c>
       <c r="N33" t="n">
         <v>16.49</v>
       </c>
       <c r="O33" t="n">
-        <v>13.334</v>
+        <v>13.33</v>
       </c>
       <c r="P33" t="n">
-        <v>13.308</v>
+        <v>13.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>13.321</v>
+        <v>13.32</v>
       </c>
     </row>
     <row r="34">
@@ -2672,49 +2672,49 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5.045</v>
+        <v>5.04</v>
       </c>
       <c r="D34" t="n">
-        <v>11.015</v>
+        <v>11.01</v>
       </c>
       <c r="E34" t="n">
-        <v>15.755</v>
+        <v>15.75</v>
       </c>
       <c r="F34" t="n">
-        <v>21.215</v>
+        <v>21.21</v>
       </c>
       <c r="G34" t="n">
-        <v>6.575</v>
+        <v>6.57</v>
       </c>
       <c r="H34" t="n">
-        <v>11.015</v>
+        <v>11.01</v>
       </c>
       <c r="I34" t="n">
-        <v>15.755</v>
+        <v>15.75</v>
       </c>
       <c r="J34" t="n">
         <v>19.43</v>
       </c>
       <c r="K34" t="n">
-        <v>9.821</v>
+        <v>9.82</v>
       </c>
       <c r="L34" t="n">
-        <v>16.847</v>
+        <v>16.84</v>
       </c>
       <c r="M34" t="n">
-        <v>10.127</v>
+        <v>10.12</v>
       </c>
       <c r="N34" t="n">
         <v>16.49</v>
       </c>
       <c r="O34" t="n">
-        <v>13.334</v>
+        <v>13.33</v>
       </c>
       <c r="P34" t="n">
-        <v>13.308</v>
+        <v>13.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>13.321</v>
+        <v>13.32</v>
       </c>
     </row>
     <row r="35">
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="D35" t="n">
         <v>9.890000000000001</v>
@@ -2736,10 +2736,10 @@
         <v>15.18</v>
       </c>
       <c r="F35" t="n">
-        <v>21.215</v>
+        <v>21.21</v>
       </c>
       <c r="G35" t="n">
-        <v>5.675</v>
+        <v>5.67</v>
       </c>
       <c r="H35" t="n">
         <v>9.890000000000001</v>
@@ -2751,25 +2751,25 @@
         <v>19.23</v>
       </c>
       <c r="K35" t="n">
-        <v>8.756</v>
+        <v>8.75</v>
       </c>
       <c r="L35" t="n">
-        <v>16.387</v>
+        <v>16.39</v>
       </c>
       <c r="M35" t="n">
-        <v>9.047000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="N35" t="n">
         <v>15.99</v>
       </c>
       <c r="O35" t="n">
-        <v>12.572</v>
+        <v>12.57</v>
       </c>
       <c r="P35" t="n">
-        <v>12.518</v>
+        <v>12.52</v>
       </c>
       <c r="Q35" t="n">
-        <v>12.545</v>
+        <v>12.54</v>
       </c>
     </row>
     <row r="36">
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="D36" t="n">
         <v>9.890000000000001</v>
@@ -2791,10 +2791,10 @@
         <v>15.18</v>
       </c>
       <c r="F36" t="n">
-        <v>21.215</v>
+        <v>21.22</v>
       </c>
       <c r="G36" t="n">
-        <v>5.675</v>
+        <v>5.67</v>
       </c>
       <c r="H36" t="n">
         <v>9.890000000000001</v>
@@ -2806,25 +2806,25 @@
         <v>19.23</v>
       </c>
       <c r="K36" t="n">
-        <v>8.756</v>
+        <v>8.75</v>
       </c>
       <c r="L36" t="n">
-        <v>16.387</v>
+        <v>16.39</v>
       </c>
       <c r="M36" t="n">
-        <v>9.047000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="N36" t="n">
         <v>15.99</v>
       </c>
       <c r="O36" t="n">
-        <v>12.572</v>
+        <v>12.57</v>
       </c>
       <c r="P36" t="n">
-        <v>12.518</v>
+        <v>12.52</v>
       </c>
       <c r="Q36" t="n">
-        <v>12.545</v>
+        <v>12.54</v>
       </c>
     </row>
     <row r="37">
@@ -2837,49 +2837,49 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.155</v>
+        <v>1.16</v>
       </c>
       <c r="D37" t="n">
-        <v>5.555</v>
+        <v>5.55</v>
       </c>
       <c r="E37" t="n">
-        <v>11.275</v>
+        <v>11.28</v>
       </c>
       <c r="F37" t="n">
-        <v>16.775</v>
+        <v>16.77</v>
       </c>
       <c r="G37" t="n">
-        <v>1.965</v>
+        <v>1.96</v>
       </c>
       <c r="H37" t="n">
-        <v>5.555</v>
+        <v>5.55</v>
       </c>
       <c r="I37" t="n">
-        <v>11.275</v>
+        <v>11.28</v>
       </c>
       <c r="J37" t="n">
         <v>15.03</v>
       </c>
       <c r="K37" t="n">
-        <v>4.675</v>
+        <v>4.67</v>
       </c>
       <c r="L37" t="n">
-        <v>12.375</v>
+        <v>12.38</v>
       </c>
       <c r="M37" t="n">
-        <v>4.837</v>
+        <v>4.83</v>
       </c>
       <c r="N37" t="n">
-        <v>12.026</v>
+        <v>12.03</v>
       </c>
       <c r="O37" t="n">
-        <v>8.525</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="P37" t="n">
-        <v>8.430999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="Q37" t="n">
-        <v>8.478</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="40">
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4.825</v>
+        <v>4.81</v>
       </c>
       <c r="D43" t="n">
         <v>9.449999999999999</v>
@@ -2972,10 +2972,10 @@
         <v>13.97</v>
       </c>
       <c r="F43" t="n">
-        <v>20.31</v>
+        <v>20.3</v>
       </c>
       <c r="G43" t="n">
-        <v>6.25</v>
+        <v>6.24</v>
       </c>
       <c r="H43" t="n">
         <v>9.449999999999999</v>
@@ -2987,25 +2987,25 @@
         <v>18.16</v>
       </c>
       <c r="K43" t="n">
-        <v>8.525</v>
+        <v>8.52</v>
       </c>
       <c r="L43" t="n">
-        <v>15.238</v>
+        <v>15.24</v>
       </c>
       <c r="M43" t="n">
         <v>8.81</v>
       </c>
       <c r="N43" t="n">
-        <v>14.808</v>
+        <v>14.81</v>
       </c>
       <c r="O43" t="n">
-        <v>11.881</v>
+        <v>11.88</v>
       </c>
       <c r="P43" t="n">
-        <v>11.809</v>
+        <v>11.81</v>
       </c>
       <c r="Q43" t="n">
-        <v>11.845</v>
+        <v>11.85</v>
       </c>
     </row>
     <row r="44">
@@ -3018,49 +3018,49 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5.045</v>
+        <v>5.05</v>
       </c>
       <c r="D44" t="n">
-        <v>9.914999999999999</v>
+        <v>9.92</v>
       </c>
       <c r="E44" t="n">
-        <v>13.555</v>
+        <v>13.56</v>
       </c>
       <c r="F44" t="n">
-        <v>18.465</v>
+        <v>18.46</v>
       </c>
       <c r="G44" t="n">
-        <v>6.429</v>
+        <v>6.42</v>
       </c>
       <c r="H44" t="n">
-        <v>9.914999999999999</v>
+        <v>9.92</v>
       </c>
       <c r="I44" t="n">
-        <v>13.555</v>
+        <v>13.56</v>
       </c>
       <c r="J44" t="n">
         <v>16.83</v>
       </c>
       <c r="K44" t="n">
-        <v>8.941000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>14.537</v>
+        <v>14.54</v>
       </c>
       <c r="M44" t="n">
-        <v>9.218</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="N44" t="n">
         <v>14.21</v>
       </c>
       <c r="O44" t="n">
-        <v>11.739</v>
+        <v>11.74</v>
       </c>
       <c r="P44" t="n">
-        <v>11.714</v>
+        <v>11.71</v>
       </c>
       <c r="Q44" t="n">
-        <v>11.727</v>
+        <v>11.73</v>
       </c>
     </row>
     <row r="45">
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="D45" t="n">
         <v>8.789999999999999</v>
@@ -3082,10 +3082,10 @@
         <v>12.98</v>
       </c>
       <c r="F45" t="n">
-        <v>18.465</v>
+        <v>18.47</v>
       </c>
       <c r="G45" t="n">
-        <v>5.529</v>
+        <v>5.52</v>
       </c>
       <c r="H45" t="n">
         <v>8.789999999999999</v>
@@ -3097,22 +3097,22 @@
         <v>16.63</v>
       </c>
       <c r="K45" t="n">
-        <v>7.876</v>
+        <v>7.87</v>
       </c>
       <c r="L45" t="n">
-        <v>14.077</v>
+        <v>14.08</v>
       </c>
       <c r="M45" t="n">
-        <v>8.138</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="N45" t="n">
         <v>13.71</v>
       </c>
       <c r="O45" t="n">
-        <v>10.976</v>
+        <v>10.97</v>
       </c>
       <c r="P45" t="n">
-        <v>10.924</v>
+        <v>10.93</v>
       </c>
       <c r="Q45" t="n">
         <v>10.95</v>
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4.495</v>
+        <v>4.49</v>
       </c>
       <c r="D46" t="n">
         <v>9.09</v>
@@ -3140,7 +3140,7 @@
         <v>17.34</v>
       </c>
       <c r="G46" t="n">
-        <v>5.635</v>
+        <v>5.63</v>
       </c>
       <c r="H46" t="n">
         <v>9.09</v>
@@ -3152,25 +3152,25 @@
         <v>15.83</v>
       </c>
       <c r="K46" t="n">
-        <v>8.170999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="L46" t="n">
-        <v>13.652</v>
+        <v>13.65</v>
       </c>
       <c r="M46" t="n">
-        <v>8.398999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="N46" t="n">
         <v>13.35</v>
       </c>
       <c r="O46" t="n">
-        <v>10.912</v>
+        <v>10.91</v>
       </c>
       <c r="P46" t="n">
-        <v>10.874</v>
+        <v>10.88</v>
       </c>
       <c r="Q46" t="n">
-        <v>10.893</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="47">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="D47" t="n">
         <v>7.14</v>
@@ -3192,10 +3192,10 @@
         <v>11.33</v>
       </c>
       <c r="F47" t="n">
-        <v>16.215</v>
+        <v>16.21</v>
       </c>
       <c r="G47" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="H47" t="n">
         <v>7.14</v>
@@ -3207,25 +3207,25 @@
         <v>14.63</v>
       </c>
       <c r="K47" t="n">
-        <v>6.226</v>
+        <v>6.22</v>
       </c>
       <c r="L47" t="n">
-        <v>12.307</v>
+        <v>12.31</v>
       </c>
       <c r="M47" t="n">
-        <v>6.454</v>
+        <v>6.45</v>
       </c>
       <c r="N47" t="n">
         <v>11.99</v>
       </c>
       <c r="O47" t="n">
-        <v>9.266999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="P47" t="n">
-        <v>9.222</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="Q47" t="n">
-        <v>9.244</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="48">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="D48" t="n">
         <v>7.14</v>
@@ -3247,10 +3247,10 @@
         <v>11.33</v>
       </c>
       <c r="F48" t="n">
-        <v>16.215</v>
+        <v>16.21</v>
       </c>
       <c r="G48" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="H48" t="n">
         <v>7.14</v>
@@ -3262,25 +3262,25 @@
         <v>14.63</v>
       </c>
       <c r="K48" t="n">
-        <v>6.226</v>
+        <v>6.22</v>
       </c>
       <c r="L48" t="n">
-        <v>12.307</v>
+        <v>12.31</v>
       </c>
       <c r="M48" t="n">
-        <v>6.454</v>
+        <v>6.45</v>
       </c>
       <c r="N48" t="n">
         <v>11.99</v>
       </c>
       <c r="O48" t="n">
-        <v>9.266999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="P48" t="n">
-        <v>9.222</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="Q48" t="n">
-        <v>9.244</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="49">
@@ -3293,49 +3293,49 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2.195</v>
+        <v>2.2</v>
       </c>
       <c r="D49" t="n">
-        <v>6.015</v>
+        <v>6.01</v>
       </c>
       <c r="E49" t="n">
-        <v>10.755</v>
+        <v>10.76</v>
       </c>
       <c r="F49" t="n">
-        <v>16.215</v>
+        <v>16.22</v>
       </c>
       <c r="G49" t="n">
-        <v>3.125</v>
+        <v>3.12</v>
       </c>
       <c r="H49" t="n">
-        <v>6.015</v>
+        <v>6.01</v>
       </c>
       <c r="I49" t="n">
-        <v>10.755</v>
+        <v>10.76</v>
       </c>
       <c r="J49" t="n">
         <v>14.43</v>
       </c>
       <c r="K49" t="n">
-        <v>5.251</v>
+        <v>5.25</v>
       </c>
       <c r="L49" t="n">
-        <v>11.847</v>
+        <v>11.85</v>
       </c>
       <c r="M49" t="n">
-        <v>5.437</v>
+        <v>5.43</v>
       </c>
       <c r="N49" t="n">
         <v>11.49</v>
       </c>
       <c r="O49" t="n">
-        <v>8.548999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="P49" t="n">
-        <v>8.462999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="Q49" t="n">
-        <v>8.506</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="50">
@@ -3348,49 +3348,49 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2.195</v>
+        <v>2.2</v>
       </c>
       <c r="D50" t="n">
-        <v>6.015</v>
+        <v>6.01</v>
       </c>
       <c r="E50" t="n">
-        <v>10.755</v>
+        <v>10.76</v>
       </c>
       <c r="F50" t="n">
-        <v>16.215</v>
+        <v>16.22</v>
       </c>
       <c r="G50" t="n">
-        <v>3.125</v>
+        <v>3.12</v>
       </c>
       <c r="H50" t="n">
-        <v>6.015</v>
+        <v>6.01</v>
       </c>
       <c r="I50" t="n">
-        <v>10.755</v>
+        <v>10.76</v>
       </c>
       <c r="J50" t="n">
         <v>14.43</v>
       </c>
       <c r="K50" t="n">
-        <v>5.251</v>
+        <v>5.25</v>
       </c>
       <c r="L50" t="n">
-        <v>11.847</v>
+        <v>11.85</v>
       </c>
       <c r="M50" t="n">
-        <v>5.437</v>
+        <v>5.43</v>
       </c>
       <c r="N50" t="n">
         <v>11.49</v>
       </c>
       <c r="O50" t="n">
-        <v>8.548999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="P50" t="n">
-        <v>8.462999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="Q50" t="n">
-        <v>8.506</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="51">
@@ -3403,49 +3403,49 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1.155</v>
+        <v>1.16</v>
       </c>
       <c r="D51" t="n">
-        <v>4.455</v>
+        <v>4.46</v>
       </c>
       <c r="E51" t="n">
-        <v>9.074999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="F51" t="n">
-        <v>14.025</v>
+        <v>14.02</v>
       </c>
       <c r="G51" t="n">
-        <v>1.819</v>
+        <v>1.81</v>
       </c>
       <c r="H51" t="n">
-        <v>4.455</v>
+        <v>4.46</v>
       </c>
       <c r="I51" t="n">
-        <v>9.074999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="J51" t="n">
         <v>12.43</v>
       </c>
       <c r="K51" t="n">
-        <v>3.795</v>
+        <v>3.8</v>
       </c>
       <c r="L51" t="n">
-        <v>10.065</v>
+        <v>10.07</v>
       </c>
       <c r="M51" t="n">
-        <v>3.928</v>
+        <v>3.93</v>
       </c>
       <c r="N51" t="n">
-        <v>9.746</v>
+        <v>9.75</v>
       </c>
       <c r="O51" t="n">
-        <v>6.93</v>
+        <v>6.94</v>
       </c>
       <c r="P51" t="n">
-        <v>6.837</v>
+        <v>6.84</v>
       </c>
       <c r="Q51" t="n">
-        <v>6.883</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="52">
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.605</v>
+        <v>0.6</v>
       </c>
       <c r="D52" t="n">
         <v>3.63</v>
@@ -3470,7 +3470,7 @@
         <v>12.9</v>
       </c>
       <c r="G52" t="n">
-        <v>1.025</v>
+        <v>1.02</v>
       </c>
       <c r="H52" t="n">
         <v>3.63</v>
@@ -3482,22 +3482,22 @@
         <v>11.43</v>
       </c>
       <c r="K52" t="n">
-        <v>3.025</v>
+        <v>3.02</v>
       </c>
       <c r="L52" t="n">
         <v>9.18</v>
       </c>
       <c r="M52" t="n">
-        <v>3.109</v>
+        <v>3.11</v>
       </c>
       <c r="N52" t="n">
-        <v>8.885999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="O52" t="n">
-        <v>6.103</v>
+        <v>6.1</v>
       </c>
       <c r="P52" t="n">
-        <v>5.997</v>
+        <v>6</v>
       </c>
       <c r="Q52" t="n">
         <v>6.05</v>
@@ -3532,10 +3532,10 @@
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>0.697</v>
+        <v>0.7</v>
       </c>
       <c r="D58" t="n">
-        <v>0.508</v>
+        <v>0.51</v>
       </c>
       <c r="F58" s="13" t="inlineStr">
         <is>
@@ -3546,47 +3546,47 @@
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>0.637</v>
+        <v>0.64</v>
       </c>
       <c r="I58" t="n">
-        <v>0.427</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>0.697</v>
+        <v>0.7</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>0.751</v>
+        <v>0.75</v>
       </c>
       <c r="G59" t="n">
-        <v>0.637</v>
+        <v>0.64</v>
       </c>
       <c r="H59" t="n">
         <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>0.733</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>0.508</v>
+        <v>0.51</v>
       </c>
       <c r="C60" t="n">
-        <v>0.751</v>
+        <v>0.75</v>
       </c>
       <c r="D60" t="n">
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>0.427</v>
+        <v>0.43</v>
       </c>
       <c r="H60" t="n">
-        <v>0.733</v>
+        <v>0.73</v>
       </c>
       <c r="I60" t="n">
         <v>1</v>
@@ -3605,7 +3605,7 @@
         <v>0.68</v>
       </c>
       <c r="D62" t="n">
-        <v>0.795</v>
+        <v>0.79</v>
       </c>
       <c r="F62" s="13" t="inlineStr">
         <is>
@@ -3616,10 +3616,10 @@
         <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>0.652</v>
+        <v>0.65</v>
       </c>
       <c r="I62" t="n">
-        <v>0.772</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="63">
@@ -3630,33 +3630,33 @@
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>0.545</v>
+        <v>0.54</v>
       </c>
       <c r="G63" t="n">
-        <v>0.652</v>
+        <v>0.65</v>
       </c>
       <c r="H63" t="n">
         <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>0.507</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>0.795</v>
+        <v>0.79</v>
       </c>
       <c r="C64" t="n">
-        <v>0.545</v>
+        <v>0.54</v>
       </c>
       <c r="D64" t="n">
         <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>0.772</v>
+        <v>0.77</v>
       </c>
       <c r="H64" t="n">
-        <v>0.507</v>
+        <v>0.51</v>
       </c>
       <c r="I64" t="n">
         <v>1</v>
@@ -3672,10 +3672,10 @@
         <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>0.267</v>
+        <v>0.27</v>
       </c>
       <c r="D66" t="n">
-        <v>0.737</v>
+        <v>0.74</v>
       </c>
       <c r="F66" s="13" t="inlineStr">
         <is>
@@ -3686,47 +3686,47 @@
         <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>0.183</v>
+        <v>0.18</v>
       </c>
       <c r="I66" t="n">
-        <v>0.678</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>0.267</v>
+        <v>0.27</v>
       </c>
       <c r="C67" t="n">
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>0.373</v>
+        <v>0.37</v>
       </c>
       <c r="G67" t="n">
-        <v>0.183</v>
+        <v>0.18</v>
       </c>
       <c r="H67" t="n">
         <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>0.299</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>0.737</v>
+        <v>0.74</v>
       </c>
       <c r="C68" t="n">
-        <v>0.373</v>
+        <v>0.37</v>
       </c>
       <c r="D68" t="n">
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0.678</v>
+        <v>0.68</v>
       </c>
       <c r="H68" t="n">
-        <v>0.299</v>
+        <v>0.3</v>
       </c>
       <c r="I68" t="n">
         <v>1</v>
@@ -3742,10 +3742,10 @@
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="D70" t="n">
-        <v>0.311</v>
+        <v>0.31</v>
       </c>
       <c r="F70" s="13" t="inlineStr">
         <is>
@@ -3756,15 +3756,15 @@
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>0.639</v>
+        <v>0.64</v>
       </c>
       <c r="I70" t="n">
-        <v>0.237</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="C71" t="n">
         <v>1</v>
@@ -3773,18 +3773,18 @@
         <v>0.2</v>
       </c>
       <c r="G71" t="n">
-        <v>0.639</v>
+        <v>0.64</v>
       </c>
       <c r="H71" t="n">
         <v>1</v>
       </c>
       <c r="I71" t="n">
-        <v>0.134</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>0.311</v>
+        <v>0.31</v>
       </c>
       <c r="C72" t="n">
         <v>0.2</v>
@@ -3793,10 +3793,10 @@
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>0.237</v>
+        <v>0.24</v>
       </c>
       <c r="H72" t="n">
-        <v>0.134</v>
+        <v>0.13</v>
       </c>
       <c r="I72" t="n">
         <v>1</v>
@@ -3812,10 +3812,10 @@
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>0.321</v>
+        <v>0.32</v>
       </c>
       <c r="D74" t="n">
-        <v>0.588</v>
+        <v>0.59</v>
       </c>
       <c r="F74" s="13" t="inlineStr">
         <is>
@@ -3834,13 +3834,13 @@
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>0.321</v>
+        <v>0.32</v>
       </c>
       <c r="C75" t="n">
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>0.135</v>
+        <v>0.13</v>
       </c>
       <c r="G75" t="n">
         <v>0.24</v>
@@ -3849,15 +3849,15 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>0.074</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>0.588</v>
+        <v>0.59</v>
       </c>
       <c r="C76" t="n">
-        <v>0.135</v>
+        <v>0.13</v>
       </c>
       <c r="D76" t="n">
         <v>1</v>
@@ -3866,7 +3866,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="H76" t="n">
-        <v>0.074</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I76" t="n">
         <v>1</v>
@@ -3882,7 +3882,7 @@
         <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>0.395</v>
+        <v>0.4</v>
       </c>
       <c r="D78" t="n">
         <v>0.29</v>
@@ -3896,30 +3896,30 @@
         <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>0.336</v>
+        <v>0.34</v>
       </c>
       <c r="I78" t="n">
-        <v>0.221</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>0.395</v>
+        <v>0.4</v>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>0.099</v>
+        <v>0.1</v>
       </c>
       <c r="G79" t="n">
-        <v>0.336</v>
+        <v>0.34</v>
       </c>
       <c r="H79" t="n">
         <v>1</v>
       </c>
       <c r="I79" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="80">
@@ -3927,16 +3927,16 @@
         <v>0.29</v>
       </c>
       <c r="C80" t="n">
-        <v>0.099</v>
+        <v>0.1</v>
       </c>
       <c r="D80" t="n">
         <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>0.221</v>
+        <v>0.22</v>
       </c>
       <c r="H80" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="I80" t="n">
         <v>1</v>
@@ -3952,10 +3952,10 @@
         <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>0.395</v>
+        <v>0.4</v>
       </c>
       <c r="D82" t="n">
-        <v>0.527</v>
+        <v>0.53</v>
       </c>
       <c r="F82" s="13" t="inlineStr">
         <is>
@@ -3966,15 +3966,15 @@
         <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>0.336</v>
+        <v>0.34</v>
       </c>
       <c r="I82" t="n">
-        <v>0.464</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>0.395</v>
+        <v>0.4</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
@@ -3983,18 +3983,18 @@
         <v>0.2</v>
       </c>
       <c r="G83" t="n">
-        <v>0.336</v>
+        <v>0.34</v>
       </c>
       <c r="H83" t="n">
         <v>1</v>
       </c>
       <c r="I83" t="n">
-        <v>0.134</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>0.527</v>
+        <v>0.53</v>
       </c>
       <c r="C84" t="n">
         <v>0.2</v>
@@ -4003,10 +4003,10 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>0.464</v>
+        <v>0.46</v>
       </c>
       <c r="H84" t="n">
-        <v>0.134</v>
+        <v>0.13</v>
       </c>
       <c r="I84" t="n">
         <v>1</v>
@@ -4022,10 +4022,10 @@
         <v>1</v>
       </c>
       <c r="C86" t="n">
-        <v>0.871</v>
+        <v>0.87</v>
       </c>
       <c r="D86" t="n">
-        <v>0.617</v>
+        <v>0.62</v>
       </c>
       <c r="F86" s="13" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>0.846</v>
+        <v>0.85</v>
       </c>
       <c r="I86" t="n">
         <v>0.57</v>
@@ -4044,30 +4044,30 @@
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>0.871</v>
+        <v>0.87</v>
       </c>
       <c r="C87" t="n">
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>0.649</v>
+        <v>0.65</v>
       </c>
       <c r="G87" t="n">
-        <v>0.846</v>
+        <v>0.85</v>
       </c>
       <c r="H87" t="n">
         <v>1</v>
       </c>
       <c r="I87" t="n">
-        <v>0.614</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="88">
       <c r="B88" t="n">
-        <v>0.617</v>
+        <v>0.62</v>
       </c>
       <c r="C88" t="n">
-        <v>0.649</v>
+        <v>0.65</v>
       </c>
       <c r="D88" t="n">
         <v>1</v>
@@ -4076,7 +4076,7 @@
         <v>0.57</v>
       </c>
       <c r="H88" t="n">
-        <v>0.614</v>
+        <v>0.61</v>
       </c>
       <c r="I88" t="n">
         <v>1</v>
@@ -4092,10 +4092,10 @@
         <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>0.633</v>
+        <v>0.63</v>
       </c>
       <c r="D90" t="n">
-        <v>0.588</v>
+        <v>0.59</v>
       </c>
       <c r="F90" s="13" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I90" t="n">
         <v>0.5600000000000001</v>
@@ -4114,30 +4114,30 @@
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>0.633</v>
+        <v>0.63</v>
       </c>
       <c r="C91" t="n">
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>0.329</v>
+        <v>0.33</v>
       </c>
       <c r="G91" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H91" t="n">
         <v>1</v>
       </c>
       <c r="I91" t="n">
-        <v>0.264</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="92">
       <c r="B92" t="n">
-        <v>0.588</v>
+        <v>0.59</v>
       </c>
       <c r="C92" t="n">
-        <v>0.329</v>
+        <v>0.33</v>
       </c>
       <c r="D92" t="n">
         <v>1</v>
@@ -4146,7 +4146,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="H92" t="n">
-        <v>0.264</v>
+        <v>0.26</v>
       </c>
       <c r="I92" t="n">
         <v>1</v>
@@ -4162,10 +4162,10 @@
         <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>0.277</v>
+        <v>0.28</v>
       </c>
       <c r="D94" t="n">
-        <v>0.527</v>
+        <v>0.53</v>
       </c>
       <c r="F94" s="13" t="inlineStr">
         <is>
@@ -4176,47 +4176,47 @@
         <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>0.206</v>
+        <v>0.21</v>
       </c>
       <c r="I94" t="n">
-        <v>0.468</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="n">
-        <v>0.277</v>
+        <v>0.28</v>
       </c>
       <c r="C95" t="n">
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G95" t="n">
-        <v>0.206</v>
+        <v>0.21</v>
       </c>
       <c r="H95" t="n">
         <v>1</v>
       </c>
       <c r="I95" t="n">
-        <v>0.502</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="96">
       <c r="B96" t="n">
-        <v>0.527</v>
+        <v>0.53</v>
       </c>
       <c r="C96" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D96" t="n">
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>0.468</v>
+        <v>0.47</v>
       </c>
       <c r="H96" t="n">
-        <v>0.502</v>
+        <v>0.5</v>
       </c>
       <c r="I96" t="n">
         <v>1</v>
@@ -4251,7 +4251,7 @@
         <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>0.649</v>
+        <v>0.65</v>
       </c>
       <c r="D102" t="n">
         <v>1</v>
@@ -4265,7 +4265,7 @@
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>0.651</v>
+        <v>0.65</v>
       </c>
       <c r="I102" t="n">
         <v>1</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="103">
       <c r="B103" t="n">
-        <v>0.649</v>
+        <v>0.65</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>0.611</v>
+        <v>0.61</v>
       </c>
       <c r="G103" t="n">
-        <v>0.651</v>
+        <v>0.65</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>0.532</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="104">
@@ -4296,7 +4296,7 @@
         <v>1</v>
       </c>
       <c r="C104" t="n">
-        <v>0.611</v>
+        <v>0.61</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
@@ -4305,7 +4305,7 @@
         <v>1</v>
       </c>
       <c r="H104" t="n">
-        <v>0.532</v>
+        <v>0.53</v>
       </c>
       <c r="I104" t="n">
         <v>0</v>
@@ -4321,10 +4321,10 @@
         <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>0.645</v>
+        <v>0.64</v>
       </c>
       <c r="D106" t="n">
-        <v>0.355</v>
+        <v>0.36</v>
       </c>
       <c r="F106" s="13" t="inlineStr">
         <is>
@@ -4335,15 +4335,15 @@
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>0.637</v>
+        <v>0.64</v>
       </c>
       <c r="I106" t="n">
-        <v>0.363</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="107">
       <c r="B107" t="n">
-        <v>0.645</v>
+        <v>0.64</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -4352,7 +4352,7 @@
         <v>1</v>
       </c>
       <c r="G107" t="n">
-        <v>0.637</v>
+        <v>0.64</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -4363,7 +4363,7 @@
     </row>
     <row r="108">
       <c r="B108" t="n">
-        <v>0.355</v>
+        <v>0.36</v>
       </c>
       <c r="C108" t="n">
         <v>1</v>
@@ -4372,7 +4372,7 @@
         <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>0.363</v>
+        <v>0.36</v>
       </c>
       <c r="H108" t="n">
         <v>1</v>
@@ -4408,7 +4408,7 @@
         <v>1</v>
       </c>
       <c r="I110" t="n">
-        <v>0.244</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="111">
@@ -4419,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>0.782</v>
+        <v>0.78</v>
       </c>
       <c r="G111" t="n">
         <v>1</v>
@@ -4436,13 +4436,13 @@
         <v>0.22</v>
       </c>
       <c r="C112" t="n">
-        <v>0.782</v>
+        <v>0.78</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.244</v>
+        <v>0.24</v>
       </c>
       <c r="H112" t="n">
         <v>0.76</v>
@@ -4461,10 +4461,10 @@
         <v>0</v>
       </c>
       <c r="C114" t="n">
-        <v>0.271</v>
+        <v>0.27</v>
       </c>
       <c r="D114" t="n">
-        <v>0.739</v>
+        <v>0.74</v>
       </c>
       <c r="F114" s="13" t="inlineStr">
         <is>
@@ -4475,15 +4475,15 @@
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>0.267</v>
+        <v>0.27</v>
       </c>
       <c r="I114" t="n">
-        <v>0.747</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="115">
       <c r="B115" t="n">
-        <v>0.271</v>
+        <v>0.27</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>0.267</v>
+        <v>0.27</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
     </row>
     <row r="116">
       <c r="B116" t="n">
-        <v>0.739</v>
+        <v>0.74</v>
       </c>
       <c r="C116" t="n">
         <v>1</v>
@@ -4512,7 +4512,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>0.747</v>
+        <v>0.75</v>
       </c>
       <c r="H116" t="n">
         <v>1</v>
@@ -4531,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>0.678</v>
+        <v>0.68</v>
       </c>
       <c r="D118" t="n">
         <v>0.35</v>
@@ -4545,15 +4545,15 @@
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>0.712</v>
+        <v>0.71</v>
       </c>
       <c r="I118" t="n">
-        <v>0.329</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="119">
       <c r="B119" t="n">
-        <v>0.678</v>
+        <v>0.68</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -4562,7 +4562,7 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0.712</v>
+        <v>0.71</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -4582,7 +4582,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.329</v>
+        <v>0.33</v>
       </c>
       <c r="H120" t="n">
         <v>1</v>
@@ -4601,10 +4601,10 @@
         <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>0.495</v>
+        <v>0.49</v>
       </c>
       <c r="D122" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F122" s="13" t="inlineStr">
         <is>
@@ -4615,15 +4615,15 @@
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>0.494</v>
+        <v>0.49</v>
       </c>
       <c r="I122" t="n">
-        <v>0.582</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="123">
       <c r="B123" t="n">
-        <v>0.495</v>
+        <v>0.49</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0.494</v>
+        <v>0.49</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -4643,7 +4643,7 @@
     </row>
     <row r="124">
       <c r="B124" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C124" t="n">
         <v>1</v>
@@ -4652,7 +4652,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.582</v>
+        <v>0.58</v>
       </c>
       <c r="H124" t="n">
         <v>1</v>
@@ -4671,10 +4671,10 @@
         <v>0</v>
       </c>
       <c r="C126" t="n">
-        <v>0.616</v>
+        <v>0.62</v>
       </c>
       <c r="D126" t="n">
-        <v>0.394</v>
+        <v>0.39</v>
       </c>
       <c r="F126" s="13" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>0.603</v>
+        <v>0.6</v>
       </c>
       <c r="I126" t="n">
         <v>0.41</v>
@@ -4693,7 +4693,7 @@
     </row>
     <row r="127">
       <c r="B127" t="n">
-        <v>0.616</v>
+        <v>0.62</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -4702,7 +4702,7 @@
         <v>1</v>
       </c>
       <c r="G127" t="n">
-        <v>0.603</v>
+        <v>0.6</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
     </row>
     <row r="128">
       <c r="B128" t="n">
-        <v>0.394</v>
+        <v>0.39</v>
       </c>
       <c r="C128" t="n">
         <v>1</v>
@@ -4741,7 +4741,7 @@
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>0.355</v>
+        <v>0.35</v>
       </c>
       <c r="D130" t="n">
         <v>1</v>
@@ -4755,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>0.381</v>
+        <v>0.38</v>
       </c>
       <c r="I130" t="n">
         <v>1</v>
@@ -4763,16 +4763,16 @@
     </row>
     <row r="131">
       <c r="B131" t="n">
-        <v>0.355</v>
+        <v>0.35</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>0.962</v>
+        <v>0.96</v>
       </c>
       <c r="G131" t="n">
-        <v>0.381</v>
+        <v>0.38</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -4786,7 +4786,7 @@
         <v>1</v>
       </c>
       <c r="C132" t="n">
-        <v>0.962</v>
+        <v>0.96</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -4811,10 +4811,10 @@
         <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>0.415</v>
+        <v>0.41</v>
       </c>
       <c r="D134" t="n">
-        <v>0.585</v>
+        <v>0.59</v>
       </c>
       <c r="F134" s="13" t="inlineStr">
         <is>
@@ -4825,15 +4825,15 @@
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>0.465</v>
+        <v>0.47</v>
       </c>
       <c r="I134" t="n">
-        <v>0.535</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="135">
       <c r="B135" t="n">
-        <v>0.415</v>
+        <v>0.41</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -4842,7 +4842,7 @@
         <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>0.465</v>
+        <v>0.47</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4853,7 +4853,7 @@
     </row>
     <row r="136">
       <c r="B136" t="n">
-        <v>0.585</v>
+        <v>0.59</v>
       </c>
       <c r="C136" t="n">
         <v>1</v>
@@ -4862,7 +4862,7 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.535</v>
+        <v>0.53</v>
       </c>
       <c r="H136" t="n">
         <v>1</v>
@@ -4898,7 +4898,7 @@
         <v>1</v>
       </c>
       <c r="I138" t="n">
-        <v>0.521</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="139">
@@ -4909,7 +4909,7 @@
         <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>0.481</v>
+        <v>0.48</v>
       </c>
       <c r="G139" t="n">
         <v>1</v>
@@ -4926,13 +4926,13 @@
         <v>0.52</v>
       </c>
       <c r="C140" t="n">
-        <v>0.481</v>
+        <v>0.48</v>
       </c>
       <c r="D140" t="n">
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.521</v>
+        <v>0.52</v>
       </c>
       <c r="H140" t="n">
         <v>0.48</v>
@@ -4970,10 +4970,10 @@
         <v>1</v>
       </c>
       <c r="C146" t="n">
-        <v>0.489</v>
+        <v>0.49</v>
       </c>
       <c r="D146" t="n">
-        <v>0.203</v>
+        <v>0.2</v>
       </c>
       <c r="F146" s="13" t="inlineStr">
         <is>
@@ -4984,47 +4984,47 @@
         <v>1</v>
       </c>
       <c r="H146" t="n">
-        <v>0.464</v>
+        <v>0.46</v>
       </c>
       <c r="I146" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="147">
       <c r="B147" t="n">
-        <v>0.489</v>
+        <v>0.49</v>
       </c>
       <c r="C147" t="n">
         <v>1</v>
       </c>
       <c r="D147" t="n">
-        <v>0.533</v>
+        <v>0.53</v>
       </c>
       <c r="G147" t="n">
-        <v>0.464</v>
+        <v>0.46</v>
       </c>
       <c r="H147" t="n">
         <v>1</v>
       </c>
       <c r="I147" t="n">
-        <v>0.574</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="148">
       <c r="B148" t="n">
-        <v>0.203</v>
+        <v>0.2</v>
       </c>
       <c r="C148" t="n">
-        <v>0.533</v>
+        <v>0.53</v>
       </c>
       <c r="D148" t="n">
         <v>1</v>
       </c>
       <c r="G148" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
       <c r="H148" t="n">
-        <v>0.574</v>
+        <v>0.57</v>
       </c>
       <c r="I148" t="n">
         <v>1</v>
@@ -5040,10 +5040,10 @@
         <v>1</v>
       </c>
       <c r="C150" t="n">
-        <v>0.485</v>
+        <v>0.49</v>
       </c>
       <c r="D150" t="n">
-        <v>0.705</v>
+        <v>0.7</v>
       </c>
       <c r="F150" s="13" t="inlineStr">
         <is>
@@ -5054,47 +5054,47 @@
         <v>1</v>
       </c>
       <c r="H150" t="n">
-        <v>0.479</v>
+        <v>0.48</v>
       </c>
       <c r="I150" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="151">
       <c r="B151" t="n">
-        <v>0.485</v>
+        <v>0.49</v>
       </c>
       <c r="C151" t="n">
         <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>0.218</v>
+        <v>0.22</v>
       </c>
       <c r="G151" t="n">
-        <v>0.479</v>
+        <v>0.48</v>
       </c>
       <c r="H151" t="n">
         <v>1</v>
       </c>
       <c r="I151" t="n">
-        <v>0.203</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="152">
       <c r="B152" t="n">
-        <v>0.705</v>
+        <v>0.7</v>
       </c>
       <c r="C152" t="n">
-        <v>0.218</v>
+        <v>0.22</v>
       </c>
       <c r="D152" t="n">
         <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H152" t="n">
-        <v>0.203</v>
+        <v>0.2</v>
       </c>
       <c r="I152" t="n">
         <v>1</v>
@@ -5110,10 +5110,10 @@
         <v>1</v>
       </c>
       <c r="C154" t="n">
-        <v>0.107</v>
+        <v>0.11</v>
       </c>
       <c r="D154" t="n">
-        <v>0.762</v>
+        <v>0.76</v>
       </c>
       <c r="F154" s="13" t="inlineStr">
         <is>
@@ -5124,15 +5124,15 @@
         <v>1</v>
       </c>
       <c r="H154" t="n">
-        <v>0.073</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I154" t="n">
-        <v>0.725</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="155">
       <c r="B155" t="n">
-        <v>0.107</v>
+        <v>0.11</v>
       </c>
       <c r="C155" t="n">
         <v>1</v>
@@ -5141,18 +5141,18 @@
         <v>0.28</v>
       </c>
       <c r="G155" t="n">
-        <v>0.073</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H155" t="n">
         <v>1</v>
       </c>
       <c r="I155" t="n">
-        <v>0.264</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="156">
       <c r="B156" t="n">
-        <v>0.762</v>
+        <v>0.76</v>
       </c>
       <c r="C156" t="n">
         <v>0.28</v>
@@ -5161,10 +5161,10 @@
         <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>0.725</v>
+        <v>0.73</v>
       </c>
       <c r="H156" t="n">
-        <v>0.264</v>
+        <v>0.26</v>
       </c>
       <c r="I156" t="n">
         <v>1</v>
@@ -5183,7 +5183,7 @@
         <v>0.71</v>
       </c>
       <c r="D158" t="n">
-        <v>0.281</v>
+        <v>0.28</v>
       </c>
       <c r="F158" s="13" t="inlineStr">
         <is>
@@ -5194,10 +5194,10 @@
         <v>1</v>
       </c>
       <c r="H158" t="n">
-        <v>0.696</v>
+        <v>0.7</v>
       </c>
       <c r="I158" t="n">
-        <v>0.246</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="159">
@@ -5211,18 +5211,18 @@
         <v>0.08</v>
       </c>
       <c r="G159" t="n">
-        <v>0.696</v>
+        <v>0.7</v>
       </c>
       <c r="H159" t="n">
         <v>1</v>
       </c>
       <c r="I159" t="n">
-        <v>0.054</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="160">
       <c r="B160" t="n">
-        <v>0.281</v>
+        <v>0.28</v>
       </c>
       <c r="C160" t="n">
         <v>0.08</v>
@@ -5231,10 +5231,10 @@
         <v>1</v>
       </c>
       <c r="G160" t="n">
-        <v>0.246</v>
+        <v>0.25</v>
       </c>
       <c r="H160" t="n">
-        <v>0.054</v>
+        <v>0.05</v>
       </c>
       <c r="I160" t="n">
         <v>1</v>
@@ -5250,10 +5250,10 @@
         <v>1</v>
       </c>
       <c r="C162" t="n">
-        <v>0.322</v>
+        <v>0.32</v>
       </c>
       <c r="D162" t="n">
-        <v>0.625</v>
+        <v>0.62</v>
       </c>
       <c r="F162" s="13" t="inlineStr">
         <is>
@@ -5264,24 +5264,24 @@
         <v>1</v>
       </c>
       <c r="H162" t="n">
-        <v>0.269</v>
+        <v>0.27</v>
       </c>
       <c r="I162" t="n">
-        <v>0.626</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="163">
       <c r="B163" t="n">
-        <v>0.322</v>
+        <v>0.32</v>
       </c>
       <c r="C163" t="n">
         <v>1</v>
       </c>
       <c r="D163" t="n">
-        <v>0.054</v>
+        <v>0.05</v>
       </c>
       <c r="G163" t="n">
-        <v>0.269</v>
+        <v>0.27</v>
       </c>
       <c r="H163" t="n">
         <v>1</v>
@@ -5292,16 +5292,16 @@
     </row>
     <row r="164">
       <c r="B164" t="n">
-        <v>0.625</v>
+        <v>0.62</v>
       </c>
       <c r="C164" t="n">
-        <v>0.054</v>
+        <v>0.05</v>
       </c>
       <c r="D164" t="n">
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>0.626</v>
+        <v>0.63</v>
       </c>
       <c r="H164" t="n">
         <v>0.03</v>
@@ -5320,10 +5320,10 @@
         <v>1</v>
       </c>
       <c r="C166" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="D166" t="n">
-        <v>0.381</v>
+        <v>0.38</v>
       </c>
       <c r="F166" s="13" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>1</v>
       </c>
       <c r="H166" t="n">
-        <v>0.438</v>
+        <v>0.44</v>
       </c>
       <c r="I166" t="n">
         <v>0.34</v>
@@ -5342,7 +5342,7 @@
     </row>
     <row r="167">
       <c r="B167" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="C167" t="n">
         <v>1</v>
@@ -5351,18 +5351,18 @@
         <v>0.04</v>
       </c>
       <c r="G167" t="n">
-        <v>0.438</v>
+        <v>0.44</v>
       </c>
       <c r="H167" t="n">
         <v>1</v>
       </c>
       <c r="I167" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="168">
       <c r="B168" t="n">
-        <v>0.381</v>
+        <v>0.38</v>
       </c>
       <c r="C168" t="n">
         <v>0.04</v>
@@ -5374,7 +5374,7 @@
         <v>0.34</v>
       </c>
       <c r="H168" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="I168" t="n">
         <v>1</v>
@@ -5390,10 +5390,10 @@
         <v>1</v>
       </c>
       <c r="C170" t="n">
-        <v>0.389</v>
+        <v>0.39</v>
       </c>
       <c r="D170" t="n">
-        <v>0.574</v>
+        <v>0.57</v>
       </c>
       <c r="F170" s="13" t="inlineStr">
         <is>
@@ -5404,15 +5404,15 @@
         <v>1</v>
       </c>
       <c r="H170" t="n">
-        <v>0.373</v>
+        <v>0.37</v>
       </c>
       <c r="I170" t="n">
-        <v>0.539</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="171">
       <c r="B171" t="n">
-        <v>0.389</v>
+        <v>0.39</v>
       </c>
       <c r="C171" t="n">
         <v>1</v>
@@ -5421,18 +5421,18 @@
         <v>0.08</v>
       </c>
       <c r="G171" t="n">
-        <v>0.373</v>
+        <v>0.37</v>
       </c>
       <c r="H171" t="n">
         <v>1</v>
       </c>
       <c r="I171" t="n">
-        <v>0.054</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="172">
       <c r="B172" t="n">
-        <v>0.574</v>
+        <v>0.57</v>
       </c>
       <c r="C172" t="n">
         <v>0.08</v>
@@ -5441,10 +5441,10 @@
         <v>1</v>
       </c>
       <c r="G172" t="n">
-        <v>0.539</v>
+        <v>0.54</v>
       </c>
       <c r="H172" t="n">
-        <v>0.054</v>
+        <v>0.05</v>
       </c>
       <c r="I172" t="n">
         <v>1</v>
@@ -5460,10 +5460,10 @@
         <v>1</v>
       </c>
       <c r="C174" t="n">
-        <v>0.735</v>
+        <v>0.74</v>
       </c>
       <c r="D174" t="n">
-        <v>0.247</v>
+        <v>0.25</v>
       </c>
       <c r="F174" s="13" t="inlineStr">
         <is>
@@ -5477,18 +5477,18 @@
         <v>0.71</v>
       </c>
       <c r="I174" t="n">
-        <v>0.228</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="175">
       <c r="B175" t="n">
-        <v>0.735</v>
+        <v>0.74</v>
       </c>
       <c r="C175" t="n">
         <v>1</v>
       </c>
       <c r="D175" t="n">
-        <v>0.283</v>
+        <v>0.28</v>
       </c>
       <c r="G175" t="n">
         <v>0.71</v>
@@ -5497,24 +5497,24 @@
         <v>1</v>
       </c>
       <c r="I175" t="n">
-        <v>0.287</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="176">
       <c r="B176" t="n">
-        <v>0.247</v>
+        <v>0.25</v>
       </c>
       <c r="C176" t="n">
-        <v>0.283</v>
+        <v>0.28</v>
       </c>
       <c r="D176" t="n">
         <v>1</v>
       </c>
       <c r="G176" t="n">
-        <v>0.228</v>
+        <v>0.23</v>
       </c>
       <c r="H176" t="n">
-        <v>0.287</v>
+        <v>0.29</v>
       </c>
       <c r="I176" t="n">
         <v>1</v>
@@ -5530,10 +5530,10 @@
         <v>1</v>
       </c>
       <c r="C178" t="n">
-        <v>0.604</v>
+        <v>0.61</v>
       </c>
       <c r="D178" t="n">
-        <v>0.484</v>
+        <v>0.48</v>
       </c>
       <c r="F178" s="13" t="inlineStr">
         <is>
@@ -5544,47 +5544,47 @@
         <v>1</v>
       </c>
       <c r="H178" t="n">
-        <v>0.546</v>
+        <v>0.55</v>
       </c>
       <c r="I178" t="n">
-        <v>0.503</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="179">
       <c r="B179" t="n">
-        <v>0.604</v>
+        <v>0.61</v>
       </c>
       <c r="C179" t="n">
         <v>1</v>
       </c>
       <c r="D179" t="n">
-        <v>0.132</v>
+        <v>0.13</v>
       </c>
       <c r="G179" t="n">
-        <v>0.546</v>
+        <v>0.55</v>
       </c>
       <c r="H179" t="n">
         <v>1</v>
       </c>
       <c r="I179" t="n">
-        <v>0.105</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="180">
       <c r="B180" t="n">
-        <v>0.484</v>
+        <v>0.48</v>
       </c>
       <c r="C180" t="n">
-        <v>0.132</v>
+        <v>0.13</v>
       </c>
       <c r="D180" t="n">
         <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>0.503</v>
+        <v>0.5</v>
       </c>
       <c r="H180" t="n">
-        <v>0.105</v>
+        <v>0.11</v>
       </c>
       <c r="I180" t="n">
         <v>1</v>
@@ -5600,10 +5600,10 @@
         <v>1</v>
       </c>
       <c r="C182" t="n">
-        <v>0.111</v>
+        <v>0.11</v>
       </c>
       <c r="D182" t="n">
-        <v>0.499</v>
+        <v>0.5</v>
       </c>
       <c r="F182" s="13" t="inlineStr">
         <is>
@@ -5614,47 +5614,47 @@
         <v>1</v>
       </c>
       <c r="H182" t="n">
-        <v>0.082</v>
+        <v>0.08</v>
       </c>
       <c r="I182" t="n">
-        <v>0.474</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="183">
       <c r="B183" t="n">
-        <v>0.111</v>
+        <v>0.11</v>
       </c>
       <c r="C183" t="n">
         <v>1</v>
       </c>
       <c r="D183" t="n">
-        <v>0.536</v>
+        <v>0.54</v>
       </c>
       <c r="G183" t="n">
-        <v>0.082</v>
+        <v>0.08</v>
       </c>
       <c r="H183" t="n">
         <v>1</v>
       </c>
       <c r="I183" t="n">
-        <v>0.513</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="184">
       <c r="B184" t="n">
-        <v>0.499</v>
+        <v>0.5</v>
       </c>
       <c r="C184" t="n">
-        <v>0.536</v>
+        <v>0.54</v>
       </c>
       <c r="D184" t="n">
         <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>0.474</v>
+        <v>0.47</v>
       </c>
       <c r="H184" t="n">
-        <v>0.513</v>
+        <v>0.51</v>
       </c>
       <c r="I184" t="n">
         <v>1</v>
@@ -5677,29 +5677,29 @@
         <v>1</v>
       </c>
       <c r="C189" t="n">
-        <v>0.477</v>
+        <v>0.48</v>
       </c>
       <c r="D189" t="n">
-        <v>0.187</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="190">
       <c r="B190" t="n">
-        <v>0.477</v>
+        <v>0.48</v>
       </c>
       <c r="C190" t="n">
         <v>1</v>
       </c>
       <c r="D190" t="n">
-        <v>0.554</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="191">
       <c r="B191" t="n">
-        <v>0.187</v>
+        <v>0.19</v>
       </c>
       <c r="C191" t="n">
-        <v>0.554</v>
+        <v>0.55</v>
       </c>
       <c r="D191" t="n">
         <v>1</v>
@@ -5715,15 +5715,15 @@
         <v>1</v>
       </c>
       <c r="C193" t="n">
-        <v>0.482</v>
+        <v>0.48</v>
       </c>
       <c r="D193" t="n">
-        <v>0.698</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="194">
       <c r="B194" t="n">
-        <v>0.482</v>
+        <v>0.48</v>
       </c>
       <c r="C194" t="n">
         <v>1</v>
@@ -5734,7 +5734,7 @@
     </row>
     <row r="195">
       <c r="B195" t="n">
-        <v>0.698</v>
+        <v>0.7</v>
       </c>
       <c r="C195" t="n">
         <v>0.21</v>
@@ -5756,7 +5756,7 @@
         <v>0.09</v>
       </c>
       <c r="D197" t="n">
-        <v>0.744</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="198">
@@ -5767,15 +5767,15 @@
         <v>1</v>
       </c>
       <c r="D198" t="n">
-        <v>0.272</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="199">
       <c r="B199" t="n">
-        <v>0.744</v>
+        <v>0.74</v>
       </c>
       <c r="C199" t="n">
-        <v>0.272</v>
+        <v>0.27</v>
       </c>
       <c r="D199" t="n">
         <v>1</v>
@@ -5791,29 +5791,29 @@
         <v>1</v>
       </c>
       <c r="C201" t="n">
-        <v>0.703</v>
+        <v>0.7</v>
       </c>
       <c r="D201" t="n">
-        <v>0.264</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="202">
       <c r="B202" t="n">
-        <v>0.703</v>
+        <v>0.7</v>
       </c>
       <c r="C202" t="n">
         <v>1</v>
       </c>
       <c r="D202" t="n">
-        <v>0.067</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="203">
       <c r="B203" t="n">
-        <v>0.264</v>
+        <v>0.26</v>
       </c>
       <c r="C203" t="n">
-        <v>0.067</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D203" t="n">
         <v>1</v>
@@ -5829,29 +5829,29 @@
         <v>1</v>
       </c>
       <c r="C205" t="n">
-        <v>0.295</v>
+        <v>0.3</v>
       </c>
       <c r="D205" t="n">
-        <v>0.626</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="206">
       <c r="B206" t="n">
-        <v>0.295</v>
+        <v>0.3</v>
       </c>
       <c r="C206" t="n">
         <v>1</v>
       </c>
       <c r="D206" t="n">
-        <v>0.042</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="207">
       <c r="B207" t="n">
-        <v>0.626</v>
+        <v>0.63</v>
       </c>
       <c r="C207" t="n">
-        <v>0.042</v>
+        <v>0.04</v>
       </c>
       <c r="D207" t="n">
         <v>1</v>
@@ -5905,29 +5905,29 @@
         <v>1</v>
       </c>
       <c r="C213" t="n">
-        <v>0.381</v>
+        <v>0.38</v>
       </c>
       <c r="D213" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="214">
       <c r="B214" t="n">
-        <v>0.381</v>
+        <v>0.38</v>
       </c>
       <c r="C214" t="n">
         <v>1</v>
       </c>
       <c r="D214" t="n">
-        <v>0.067</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="215">
       <c r="B215" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C215" t="n">
-        <v>0.067</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D215" t="n">
         <v>1</v>
@@ -5943,29 +5943,29 @@
         <v>1</v>
       </c>
       <c r="C217" t="n">
-        <v>0.723</v>
+        <v>0.72</v>
       </c>
       <c r="D217" t="n">
-        <v>0.237</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="218">
       <c r="B218" t="n">
-        <v>0.723</v>
+        <v>0.72</v>
       </c>
       <c r="C218" t="n">
         <v>1</v>
       </c>
       <c r="D218" t="n">
-        <v>0.285</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="219">
       <c r="B219" t="n">
-        <v>0.237</v>
+        <v>0.24</v>
       </c>
       <c r="C219" t="n">
-        <v>0.285</v>
+        <v>0.29</v>
       </c>
       <c r="D219" t="n">
         <v>1</v>
@@ -5981,29 +5981,29 @@
         <v>1</v>
       </c>
       <c r="C221" t="n">
-        <v>0.575</v>
+        <v>0.58</v>
       </c>
       <c r="D221" t="n">
-        <v>0.494</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="222">
       <c r="B222" t="n">
-        <v>0.575</v>
+        <v>0.58</v>
       </c>
       <c r="C222" t="n">
         <v>1</v>
       </c>
       <c r="D222" t="n">
-        <v>0.119</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="223">
       <c r="B223" t="n">
-        <v>0.494</v>
+        <v>0.49</v>
       </c>
       <c r="C223" t="n">
-        <v>0.119</v>
+        <v>0.12</v>
       </c>
       <c r="D223" t="n">
         <v>1</v>
@@ -6019,29 +6019,29 @@
         <v>1</v>
       </c>
       <c r="C225" t="n">
-        <v>0.097</v>
+        <v>0.1</v>
       </c>
       <c r="D225" t="n">
-        <v>0.487</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="226">
       <c r="B226" t="n">
-        <v>0.097</v>
+        <v>0.1</v>
       </c>
       <c r="C226" t="n">
         <v>1</v>
       </c>
       <c r="D226" t="n">
-        <v>0.525</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="227">
       <c r="B227" t="n">
-        <v>0.487</v>
+        <v>0.49</v>
       </c>
       <c r="C227" t="n">
-        <v>0.525</v>
+        <v>0.52</v>
       </c>
       <c r="D227" t="n">
         <v>1</v>
@@ -6061,13 +6061,13 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.517806</v>
+        <v>0.52</v>
       </c>
       <c r="C232" t="n">
-        <v>0.664453</v>
+        <v>0.66</v>
       </c>
       <c r="D232" t="n">
-        <v>0.622192</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="233">
@@ -6077,13 +6077,13 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.723765</v>
+        <v>0.72</v>
       </c>
       <c r="C233" t="n">
-        <v>0.528664</v>
+        <v>0.53</v>
       </c>
       <c r="D233" t="n">
-        <v>0.672535</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="234">
@@ -6093,13 +6093,13 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.624425</v>
+        <v>0.62</v>
       </c>
       <c r="C234" t="n">
-        <v>0.435611</v>
+        <v>0.44</v>
       </c>
       <c r="D234" t="n">
-        <v>0.704557</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="235">
@@ -6109,13 +6109,13 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.616368</v>
+        <v>0.62</v>
       </c>
       <c r="C235" t="n">
-        <v>0.53765</v>
+        <v>0.54</v>
       </c>
       <c r="D235" t="n">
-        <v>0.499132</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="236">
@@ -6125,13 +6125,13 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.638868</v>
+        <v>0.64</v>
       </c>
       <c r="C236" t="n">
-        <v>0.405288</v>
+        <v>0.41</v>
       </c>
       <c r="D236" t="n">
-        <v>0.6001919999999999</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="237">
@@ -6141,13 +6141,13 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.578981</v>
+        <v>0.58</v>
       </c>
       <c r="C237" t="n">
-        <v>0.44671</v>
+        <v>0.45</v>
       </c>
       <c r="D237" t="n">
-        <v>0.516954</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="238">
@@ -6157,13 +6157,13 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.636896</v>
+        <v>0.64</v>
       </c>
       <c r="C238" t="n">
-        <v>0.440905</v>
+        <v>0.44</v>
       </c>
       <c r="D238" t="n">
-        <v>0.587086</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="239">
@@ -6173,13 +6173,13 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.61171</v>
+        <v>0.61</v>
       </c>
       <c r="C239" t="n">
-        <v>0.6308319999999999</v>
+        <v>0.63</v>
       </c>
       <c r="D239" t="n">
-        <v>0.5567530000000001</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="240">
@@ -6189,13 +6189,13 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.670028</v>
+        <v>0.67</v>
       </c>
       <c r="C240" t="n">
-        <v>0.519979</v>
+        <v>0.52</v>
       </c>
       <c r="D240" t="n">
-        <v>0.583637</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="241">
@@ -6205,13 +6205,13 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.523666</v>
+        <v>0.52</v>
       </c>
       <c r="C241" t="n">
-        <v>0.538791</v>
+        <v>0.54</v>
       </c>
       <c r="D241" t="n">
-        <v>0.703371</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="244">
@@ -6228,13 +6228,13 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.28696</v>
+        <v>0.29</v>
       </c>
       <c r="C246" t="n">
-        <v>0.36823</v>
+        <v>0.37</v>
       </c>
       <c r="D246" t="n">
-        <v>0.34481</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="247">
@@ -6244,13 +6244,13 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.375989</v>
+        <v>0.38</v>
       </c>
       <c r="C247" t="n">
-        <v>0.274636</v>
+        <v>0.27</v>
       </c>
       <c r="D247" t="n">
-        <v>0.349375</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="248">
@@ -6260,13 +6260,13 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.353864</v>
+        <v>0.35</v>
       </c>
       <c r="C248" t="n">
-        <v>0.246862</v>
+        <v>0.25</v>
       </c>
       <c r="D248" t="n">
-        <v>0.399275</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="249">
@@ -6276,13 +6276,13 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.372845</v>
+        <v>0.37</v>
       </c>
       <c r="C249" t="n">
-        <v>0.325228</v>
+        <v>0.33</v>
       </c>
       <c r="D249" t="n">
-        <v>0.301928</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="250">
@@ -6292,13 +6292,13 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.388524</v>
+        <v>0.39</v>
       </c>
       <c r="C250" t="n">
-        <v>0.246473</v>
+        <v>0.25</v>
       </c>
       <c r="D250" t="n">
-        <v>0.365003</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="251">
@@ -6308,13 +6308,13 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.375317</v>
+        <v>0.38</v>
       </c>
       <c r="C251" t="n">
-        <v>0.289574</v>
+        <v>0.29</v>
       </c>
       <c r="D251" t="n">
-        <v>0.335109</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="252">
@@ -6324,13 +6324,13 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.382546</v>
+        <v>0.38</v>
       </c>
       <c r="C252" t="n">
-        <v>0.264826</v>
+        <v>0.26</v>
       </c>
       <c r="D252" t="n">
-        <v>0.352628</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="253">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.339972</v>
+        <v>0.34</v>
       </c>
       <c r="C253" t="n">
-        <v>0.350599</v>
+        <v>0.35</v>
       </c>
       <c r="D253" t="n">
-        <v>0.309429</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="254">
@@ -6356,13 +6356,13 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.377769</v>
+        <v>0.38</v>
       </c>
       <c r="C254" t="n">
-        <v>0.29317</v>
+        <v>0.29</v>
       </c>
       <c r="D254" t="n">
-        <v>0.329061</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="255">
@@ -6372,13 +6372,13 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.296555</v>
+        <v>0.3</v>
       </c>
       <c r="C255" t="n">
-        <v>0.305121</v>
+        <v>0.31</v>
       </c>
       <c r="D255" t="n">
-        <v>0.398324</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="258">
@@ -6462,49 +6462,49 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>5.148</v>
+        <v>5.14</v>
       </c>
       <c r="D261" t="n">
-        <v>10.677</v>
+        <v>10.68</v>
       </c>
       <c r="E261" t="n">
-        <v>14.801</v>
+        <v>14.81</v>
       </c>
       <c r="F261" t="n">
-        <v>20.106</v>
+        <v>20.11</v>
       </c>
       <c r="G261" t="n">
-        <v>6.695</v>
+        <v>6.69</v>
       </c>
       <c r="H261" t="n">
-        <v>10.677</v>
+        <v>10.68</v>
       </c>
       <c r="I261" t="n">
-        <v>14.801</v>
+        <v>14.81</v>
       </c>
       <c r="J261" t="n">
-        <v>18.345</v>
+        <v>18.34</v>
       </c>
       <c r="K261" t="n">
-        <v>9.571</v>
+        <v>9.57</v>
       </c>
       <c r="L261" t="n">
-        <v>15.862</v>
+        <v>15.87</v>
       </c>
       <c r="M261" t="n">
-        <v>9.881</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="N261" t="n">
-        <v>15.51</v>
+        <v>15.52</v>
       </c>
       <c r="O261" t="n">
-        <v>12.716</v>
+        <v>12.72</v>
       </c>
       <c r="P261" t="n">
-        <v>12.695</v>
+        <v>12.7</v>
       </c>
       <c r="Q261" t="n">
-        <v>12.706</v>
+        <v>12.71</v>
       </c>
     </row>
     <row r="262">
@@ -6517,49 +6517,49 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>5.15</v>
+        <v>5.14</v>
       </c>
       <c r="D262" t="n">
-        <v>9.689</v>
+        <v>9.69</v>
       </c>
       <c r="E262" t="n">
-        <v>14.615</v>
+        <v>14.62</v>
       </c>
       <c r="F262" t="n">
-        <v>21.422</v>
+        <v>21.42</v>
       </c>
       <c r="G262" t="n">
-        <v>6.543</v>
+        <v>6.54</v>
       </c>
       <c r="H262" t="n">
-        <v>9.689</v>
+        <v>9.69</v>
       </c>
       <c r="I262" t="n">
-        <v>14.615</v>
+        <v>14.62</v>
       </c>
       <c r="J262" t="n">
-        <v>19.108</v>
+        <v>19.11</v>
       </c>
       <c r="K262" t="n">
-        <v>8.781000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="L262" t="n">
-        <v>15.976</v>
+        <v>15.98</v>
       </c>
       <c r="M262" t="n">
         <v>9.06</v>
       </c>
       <c r="N262" t="n">
-        <v>15.514</v>
+        <v>15.52</v>
       </c>
       <c r="O262" t="n">
-        <v>12.379</v>
+        <v>12.38</v>
       </c>
       <c r="P262" t="n">
-        <v>12.287</v>
+        <v>12.29</v>
       </c>
       <c r="Q262" t="n">
-        <v>12.333</v>
+        <v>12.34</v>
       </c>
     </row>
     <row r="263">
@@ -6572,49 +6572,49 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>4.659</v>
+        <v>4.65</v>
       </c>
       <c r="D263" t="n">
-        <v>9.798999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E263" t="n">
-        <v>14.245</v>
+        <v>14.24</v>
       </c>
       <c r="F263" t="n">
-        <v>19.825</v>
+        <v>19.83</v>
       </c>
       <c r="G263" t="n">
-        <v>6.058</v>
+        <v>6.05</v>
       </c>
       <c r="H263" t="n">
-        <v>9.798999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I263" t="n">
-        <v>14.245</v>
+        <v>14.24</v>
       </c>
       <c r="J263" t="n">
-        <v>17.974</v>
+        <v>17.97</v>
       </c>
       <c r="K263" t="n">
-        <v>8.771000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="L263" t="n">
-        <v>15.361</v>
+        <v>15.36</v>
       </c>
       <c r="M263" t="n">
-        <v>9.051</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="N263" t="n">
-        <v>14.991</v>
+        <v>14.99</v>
       </c>
       <c r="O263" t="n">
-        <v>12.066</v>
+        <v>12.06</v>
       </c>
       <c r="P263" t="n">
-        <v>12.021</v>
+        <v>12.02</v>
       </c>
       <c r="Q263" t="n">
-        <v>12.044</v>
+        <v>12.04</v>
       </c>
     </row>
     <row r="264">
@@ -6627,49 +6627,49 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>4.769</v>
+        <v>4.77</v>
       </c>
       <c r="D264" t="n">
-        <v>9.609999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="E264" t="n">
-        <v>14.062</v>
+        <v>14.07</v>
       </c>
       <c r="F264" t="n">
-        <v>19.734</v>
+        <v>19.73</v>
       </c>
       <c r="G264" t="n">
-        <v>6.082</v>
+        <v>6.07</v>
       </c>
       <c r="H264" t="n">
-        <v>9.609999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="I264" t="n">
-        <v>14.062</v>
+        <v>14.07</v>
       </c>
       <c r="J264" t="n">
-        <v>17.846</v>
+        <v>17.85</v>
       </c>
       <c r="K264" t="n">
-        <v>8.641999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L264" t="n">
-        <v>15.196</v>
+        <v>15.2</v>
       </c>
       <c r="M264" t="n">
-        <v>8.904</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="N264" t="n">
-        <v>14.819</v>
+        <v>14.83</v>
       </c>
       <c r="O264" t="n">
-        <v>11.919</v>
+        <v>11.91</v>
       </c>
       <c r="P264" t="n">
-        <v>11.861</v>
+        <v>11.86</v>
       </c>
       <c r="Q264" t="n">
-        <v>11.89</v>
+        <v>11.88</v>
       </c>
     </row>
     <row r="265">
@@ -6682,49 +6682,49 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>4.466</v>
+        <v>4.46</v>
       </c>
       <c r="D265" t="n">
-        <v>9.124000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="E265" t="n">
-        <v>13.873</v>
+        <v>13.87</v>
       </c>
       <c r="F265" t="n">
-        <v>20.048</v>
+        <v>20.05</v>
       </c>
       <c r="G265" t="n">
-        <v>5.802</v>
+        <v>5.8</v>
       </c>
       <c r="H265" t="n">
-        <v>9.124000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="I265" t="n">
-        <v>13.873</v>
+        <v>13.87</v>
       </c>
       <c r="J265" t="n">
-        <v>17.977</v>
+        <v>17.98</v>
       </c>
       <c r="K265" t="n">
-        <v>8.192</v>
+        <v>8.19</v>
       </c>
       <c r="L265" t="n">
-        <v>15.108</v>
+        <v>15.11</v>
       </c>
       <c r="M265" t="n">
         <v>8.460000000000001</v>
       </c>
       <c r="N265" t="n">
-        <v>14.694</v>
+        <v>14.69</v>
       </c>
       <c r="O265" t="n">
         <v>11.65</v>
       </c>
       <c r="P265" t="n">
-        <v>11.577</v>
+        <v>11.57</v>
       </c>
       <c r="Q265" t="n">
-        <v>11.614</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="266">
@@ -6737,49 +6737,49 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>4.006</v>
+        <v>4</v>
       </c>
       <c r="D266" t="n">
-        <v>8.723000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="E266" t="n">
-        <v>13.407</v>
+        <v>13.41</v>
       </c>
       <c r="F266" t="n">
-        <v>19.228</v>
+        <v>19.23</v>
       </c>
       <c r="G266" t="n">
-        <v>5.289</v>
+        <v>5.29</v>
       </c>
       <c r="H266" t="n">
-        <v>8.723000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="I266" t="n">
-        <v>13.407</v>
+        <v>13.41</v>
       </c>
       <c r="J266" t="n">
-        <v>17.295</v>
+        <v>17.29</v>
       </c>
       <c r="K266" t="n">
         <v>7.78</v>
       </c>
       <c r="L266" t="n">
-        <v>14.571</v>
+        <v>14.57</v>
       </c>
       <c r="M266" t="n">
-        <v>8.036</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="N266" t="n">
-        <v>14.185</v>
+        <v>14.19</v>
       </c>
       <c r="O266" t="n">
-        <v>11.175</v>
+        <v>11.18</v>
       </c>
       <c r="P266" t="n">
-        <v>11.111</v>
+        <v>11.11</v>
       </c>
       <c r="Q266" t="n">
-        <v>11.143</v>
+        <v>11.14</v>
       </c>
     </row>
     <row r="267">
@@ -6792,49 +6792,49 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>3.871</v>
+        <v>3.87</v>
       </c>
       <c r="D267" t="n">
-        <v>8.646000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="E267" t="n">
-        <v>13.166</v>
+        <v>13.17</v>
       </c>
       <c r="F267" t="n">
-        <v>18.637</v>
+        <v>18.64</v>
       </c>
       <c r="G267" t="n">
-        <v>5.135</v>
+        <v>5.14</v>
       </c>
       <c r="H267" t="n">
-        <v>8.646000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="I267" t="n">
-        <v>13.166</v>
+        <v>13.17</v>
       </c>
       <c r="J267" t="n">
-        <v>16.832</v>
+        <v>16.83</v>
       </c>
       <c r="K267" t="n">
-        <v>7.691</v>
+        <v>7.69</v>
       </c>
       <c r="L267" t="n">
         <v>14.26</v>
       </c>
       <c r="M267" t="n">
-        <v>7.944</v>
+        <v>7.94</v>
       </c>
       <c r="N267" t="n">
-        <v>13.899</v>
+        <v>13.9</v>
       </c>
       <c r="O267" t="n">
-        <v>10.976</v>
+        <v>10.97</v>
       </c>
       <c r="P267" t="n">
-        <v>10.921</v>
+        <v>10.92</v>
       </c>
       <c r="Q267" t="n">
-        <v>10.948</v>
+        <v>10.95</v>
       </c>
     </row>
     <row r="268">
@@ -6847,49 +6847,49 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>4.121</v>
+        <v>4.13</v>
       </c>
       <c r="D268" t="n">
-        <v>8.734</v>
+        <v>8.74</v>
       </c>
       <c r="E268" t="n">
-        <v>13.054</v>
+        <v>13.05</v>
       </c>
       <c r="F268" t="n">
-        <v>18.267</v>
+        <v>18.27</v>
       </c>
       <c r="G268" t="n">
-        <v>5.271</v>
+        <v>5.26</v>
       </c>
       <c r="H268" t="n">
-        <v>8.734</v>
+        <v>8.74</v>
       </c>
       <c r="I268" t="n">
-        <v>13.054</v>
+        <v>13.05</v>
       </c>
       <c r="J268" t="n">
-        <v>16.554</v>
+        <v>16.56</v>
       </c>
       <c r="K268" t="n">
-        <v>7.811</v>
+        <v>7.82</v>
       </c>
       <c r="L268" t="n">
-        <v>14.097</v>
+        <v>14.09</v>
       </c>
       <c r="M268" t="n">
-        <v>8.041</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="N268" t="n">
-        <v>13.754</v>
+        <v>13.75</v>
       </c>
       <c r="O268" t="n">
-        <v>10.954</v>
+        <v>10.96</v>
       </c>
       <c r="P268" t="n">
-        <v>10.898</v>
+        <v>10.89</v>
       </c>
       <c r="Q268" t="n">
-        <v>10.926</v>
+        <v>10.93</v>
       </c>
     </row>
     <row r="269">
@@ -6902,49 +6902,49 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>3.853</v>
+        <v>3.86</v>
       </c>
       <c r="D269" t="n">
-        <v>8.334</v>
+        <v>8.33</v>
       </c>
       <c r="E269" t="n">
         <v>12.62</v>
       </c>
       <c r="F269" t="n">
-        <v>17.677</v>
+        <v>17.68</v>
       </c>
       <c r="G269" t="n">
-        <v>4.926</v>
+        <v>4.92</v>
       </c>
       <c r="H269" t="n">
-        <v>8.334</v>
+        <v>8.33</v>
       </c>
       <c r="I269" t="n">
         <v>12.62</v>
       </c>
       <c r="J269" t="n">
-        <v>16.022</v>
+        <v>16.03</v>
       </c>
       <c r="K269" t="n">
-        <v>7.438</v>
+        <v>7.44</v>
       </c>
       <c r="L269" t="n">
-        <v>13.631</v>
+        <v>13.63</v>
       </c>
       <c r="M269" t="n">
-        <v>7.652</v>
+        <v>7.65</v>
       </c>
       <c r="N269" t="n">
         <v>13.3</v>
       </c>
       <c r="O269" t="n">
-        <v>10.534</v>
+        <v>10.54</v>
       </c>
       <c r="P269" t="n">
-        <v>10.476</v>
+        <v>10.48</v>
       </c>
       <c r="Q269" t="n">
-        <v>10.505</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="270">
@@ -6957,46 +6957,46 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>0.962</v>
+        <v>0.97</v>
       </c>
       <c r="D270" t="n">
-        <v>4.469</v>
+        <v>4.47</v>
       </c>
       <c r="E270" t="n">
-        <v>9.391</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="F270" t="n">
-        <v>14.387</v>
+        <v>14.39</v>
       </c>
       <c r="G270" t="n">
-        <v>1.582</v>
+        <v>1.58</v>
       </c>
       <c r="H270" t="n">
-        <v>4.469</v>
+        <v>4.47</v>
       </c>
       <c r="I270" t="n">
-        <v>9.391</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="J270" t="n">
-        <v>12.795</v>
+        <v>12.79</v>
       </c>
       <c r="K270" t="n">
-        <v>3.768</v>
+        <v>3.77</v>
       </c>
       <c r="L270" t="n">
         <v>10.39</v>
       </c>
       <c r="M270" t="n">
-        <v>3.892</v>
+        <v>3.89</v>
       </c>
       <c r="N270" t="n">
-        <v>10.072</v>
+        <v>10.07</v>
       </c>
       <c r="O270" t="n">
-        <v>7.079</v>
+        <v>7.08</v>
       </c>
       <c r="P270" t="n">
-        <v>6.982</v>
+        <v>6.98</v>
       </c>
       <c r="Q270" t="n">
         <v>7.03</v>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_Lu 2006.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_Lu 2006.xlsx
@@ -2030,7 +2030,7 @@
   <dimension ref="A1:R373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
@@ -2157,7 +2157,7 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>2) Параметры алгоритма</t>
+          <t>2) Гиперпараметры модели</t>
         </is>
       </c>
       <c r="B10" s="13" t="n"/>
@@ -2166,7 +2166,7 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Уровень alpha-среза</t>
+          <t>alpha (уровень альфа-среза)</t>
         </is>
       </c>
       <c r="B11" s="17" t="n">
@@ -2186,7 +2186,7 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>Параметр CLTR a</t>
+          <t>a (редукция типа CLTR)</t>
         </is>
       </c>
       <c r="B13" s="17" t="n">

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_Lu 2006.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_Lu 2006.xlsx
@@ -2036,7 +2036,7 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
@@ -4357,15 +4357,15 @@
       <c r="J58" s="13" t="n"/>
       <c r="K58" s="13" t="n"/>
     </row>
-    <row r="59" ht="24" customHeight="1">
+    <row r="59" ht="18" customHeight="1">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>Матрицы согласия по верхним функциям принадлежности (AM_UMF)</t>
+          <t>AM_UMF</t>
         </is>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>Матрицы согласия по нижним функциям принадлежности (AM_LMF)</t>
+          <t>AM_LMF</t>
         </is>
       </c>
     </row>
@@ -5747,15 +5747,15 @@
       <c r="J131" s="13" t="n"/>
       <c r="K131" s="13" t="n"/>
     </row>
-    <row r="132" ht="24" customHeight="1">
+    <row r="132" ht="18" customHeight="1">
       <c r="A132" s="12" t="inlineStr">
         <is>
-          <t>Матрицы согласия по верхним функциям принадлежности (dM_UMF)</t>
+          <t>dM_UMF</t>
         </is>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
-          <t>Матрицы согласия по нижним функциям принадлежности (dM_LMF)</t>
+          <t>dM_LMF</t>
         </is>
       </c>
     </row>
@@ -7137,15 +7137,15 @@
       <c r="J204" s="13" t="n"/>
       <c r="K204" s="13" t="n"/>
     </row>
-    <row r="205" ht="24" customHeight="1">
+    <row r="205" ht="18" customHeight="1">
       <c r="A205" s="12" t="inlineStr">
         <is>
-          <t>Матрицы согласия по верхним функциям принадлежности (R_UMF)</t>
+          <t>R_UMF</t>
         </is>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
-          <t>Матрицы согласия по нижним функциям принадлежности (R_LMF)</t>
+          <t>R_LMF</t>
         </is>
       </c>
     </row>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_Lu 2006.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_Lu 2006.xlsx
@@ -2157,7 +2157,7 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>2) Гиперпараметры модели</t>
+          <t>2) Параметры модели</t>
         </is>
       </c>
       <c r="B10" s="13" t="n"/>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_Lu 2006.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_Lu 2006.xlsx
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="B12" s="17" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -7204,10 +7204,10 @@
         <v>1</v>
       </c>
       <c r="C209" s="17" t="n">
-        <v>0.199557446774999</v>
+        <v>0.2488170855468344</v>
       </c>
       <c r="D209" s="17" t="n">
-        <v>0.1978914486528676</v>
+        <v>0.2473643108160845</v>
       </c>
       <c r="G209" s="13" t="inlineStr">
         <is>
@@ -7218,10 +7218,10 @@
         <v>1</v>
       </c>
       <c r="I209" s="17" t="n">
-        <v>0.170212765957443</v>
+        <v>0.2127659574468038</v>
       </c>
       <c r="J209" s="17" t="n">
-        <v>0.170212765957443</v>
+        <v>0.2127659574468038</v>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
@@ -7231,13 +7231,13 @@
         </is>
       </c>
       <c r="B210" s="17" t="n">
-        <v>0.199557446774999</v>
+        <v>0.2488170855468344</v>
       </c>
       <c r="C210" s="17" t="n">
         <v>1</v>
       </c>
       <c r="D210" s="17" t="n">
-        <v>0.9980807098624696</v>
+        <v>0.9982306102500013</v>
       </c>
       <c r="G210" s="13" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="H210" s="17" t="n">
-        <v>0.170212765957443</v>
+        <v>0.2127659574468038</v>
       </c>
       <c r="I210" s="17" t="n">
         <v>1</v>
@@ -7261,10 +7261,10 @@
         </is>
       </c>
       <c r="B211" s="17" t="n">
-        <v>0.1978914486528676</v>
+        <v>0.2473643108160845</v>
       </c>
       <c r="C211" s="17" t="n">
-        <v>0.9980807098624696</v>
+        <v>0.9982306102500013</v>
       </c>
       <c r="D211" s="17" t="n">
         <v>1</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="H211" s="17" t="n">
-        <v>0.170212765957443</v>
+        <v>0.2127659574468038</v>
       </c>
       <c r="I211" s="17" t="n">
         <v>1</v>
@@ -7340,10 +7340,10 @@
         <v>1</v>
       </c>
       <c r="C216" s="17" t="n">
-        <v>0.7957576302257396</v>
+        <v>0.8041333122919787</v>
       </c>
       <c r="D216" s="17" t="n">
-        <v>0.249035812672177</v>
+        <v>0.3112947658402212</v>
       </c>
       <c r="G216" s="13" t="inlineStr">
         <is>
@@ -7354,10 +7354,10 @@
         <v>1</v>
       </c>
       <c r="I216" s="17" t="n">
-        <v>0.7488830664009709</v>
+        <v>0.757590761105788</v>
       </c>
       <c r="J216" s="17" t="n">
-        <v>0.2322141946451271</v>
+        <v>0.2902677433064089</v>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
@@ -7367,13 +7367,13 @@
         </is>
       </c>
       <c r="B217" s="17" t="n">
-        <v>0.7957576302257396</v>
+        <v>0.8041333122919787</v>
       </c>
       <c r="C217" s="17" t="n">
         <v>1</v>
       </c>
       <c r="D217" s="17" t="n">
-        <v>0.2600144241565769</v>
+        <v>0.31945296170257</v>
       </c>
       <c r="G217" s="13" t="inlineStr">
         <is>
@@ -7381,13 +7381,13 @@
         </is>
       </c>
       <c r="H217" s="17" t="n">
-        <v>0.7488830664009709</v>
+        <v>0.757590761105788</v>
       </c>
       <c r="I217" s="17" t="n">
         <v>1</v>
       </c>
       <c r="J217" s="17" t="n">
-        <v>0.2305571331981055</v>
+        <v>0.2861539328375007</v>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
@@ -7397,10 +7397,10 @@
         </is>
       </c>
       <c r="B218" s="17" t="n">
-        <v>0.249035812672177</v>
+        <v>0.3112947658402212</v>
       </c>
       <c r="C218" s="17" t="n">
-        <v>0.2600144241565769</v>
+        <v>0.31945296170257</v>
       </c>
       <c r="D218" s="17" t="n">
         <v>1</v>
@@ -7411,10 +7411,10 @@
         </is>
       </c>
       <c r="H218" s="17" t="n">
-        <v>0.2322141946451271</v>
+        <v>0.2902677433064089</v>
       </c>
       <c r="I218" s="17" t="n">
-        <v>0.2305571331981055</v>
+        <v>0.2861539328375007</v>
       </c>
       <c r="J218" s="17" t="n">
         <v>1</v>
@@ -7476,10 +7476,10 @@
         <v>1</v>
       </c>
       <c r="C223" s="17" t="n">
-        <v>0.2180608365019014</v>
+        <v>0.2725760456273768</v>
       </c>
       <c r="D223" s="17" t="n">
-        <v>0.7751309679521599</v>
+        <v>0.7786677985566086</v>
       </c>
       <c r="G223" s="13" t="inlineStr">
         <is>
@@ -7490,10 +7490,10 @@
         <v>1</v>
       </c>
       <c r="I223" s="17" t="n">
-        <v>0.1958506224066388</v>
+        <v>0.2448132780082985</v>
       </c>
       <c r="J223" s="17" t="n">
-        <v>0.7196777261791532</v>
+        <v>0.7213184691993512</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
@@ -7503,13 +7503,13 @@
         </is>
       </c>
       <c r="B224" s="17" t="n">
-        <v>0.2180608365019014</v>
+        <v>0.2725760456273768</v>
       </c>
       <c r="C224" s="17" t="n">
         <v>1</v>
       </c>
       <c r="D224" s="17" t="n">
-        <v>0.2270821127197437</v>
+        <v>0.2778492103679473</v>
       </c>
       <c r="G224" s="13" t="inlineStr">
         <is>
@@ -7517,13 +7517,13 @@
         </is>
       </c>
       <c r="H224" s="17" t="n">
-        <v>0.1958506224066388</v>
+        <v>0.2448132780082985</v>
       </c>
       <c r="I224" s="17" t="n">
         <v>1</v>
       </c>
       <c r="J224" s="17" t="n">
-        <v>0.1889180327868861</v>
+        <v>0.2340983606557388</v>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
@@ -7533,10 +7533,10 @@
         </is>
       </c>
       <c r="B225" s="17" t="n">
-        <v>0.7751309679521599</v>
+        <v>0.7786677985566086</v>
       </c>
       <c r="C225" s="17" t="n">
-        <v>0.2270821127197437</v>
+        <v>0.2778492103679473</v>
       </c>
       <c r="D225" s="17" t="n">
         <v>1</v>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="H225" s="17" t="n">
-        <v>0.7196777261791532</v>
+        <v>0.7213184691993512</v>
       </c>
       <c r="I225" s="17" t="n">
-        <v>0.1889180327868861</v>
+        <v>0.2340983606557388</v>
       </c>
       <c r="J225" s="17" t="n">
         <v>1</v>
@@ -7612,10 +7612,10 @@
         <v>1</v>
       </c>
       <c r="C230" s="17" t="n">
-        <v>0.846614967667577</v>
+        <v>0.8514367810384573</v>
       </c>
       <c r="D230" s="17" t="n">
-        <v>0.2338901506020283</v>
+        <v>0.2880256374470839</v>
       </c>
       <c r="G230" s="13" t="inlineStr">
         <is>
@@ -7626,10 +7626,10 @@
         <v>1</v>
       </c>
       <c r="I230" s="17" t="n">
-        <v>0.8136028083696719</v>
+        <v>0.818405379620966</v>
       </c>
       <c r="J230" s="17" t="n">
-        <v>0.2055301107879665</v>
+        <v>0.2551603020363578</v>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
@@ -7639,13 +7639,13 @@
         </is>
       </c>
       <c r="B231" s="17" t="n">
-        <v>0.846614967667577</v>
+        <v>0.8514367810384573</v>
       </c>
       <c r="C231" s="17" t="n">
         <v>1</v>
       </c>
       <c r="D231" s="17" t="n">
-        <v>0.2094493783303767</v>
+        <v>0.2618117229129708</v>
       </c>
       <c r="G231" s="13" t="inlineStr">
         <is>
@@ -7653,13 +7653,13 @@
         </is>
       </c>
       <c r="H231" s="17" t="n">
-        <v>0.8136028083696719</v>
+        <v>0.818405379620966</v>
       </c>
       <c r="I231" s="17" t="n">
         <v>1</v>
       </c>
       <c r="J231" s="17" t="n">
-        <v>0.184412563008924</v>
+        <v>0.230515703761155</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
@@ -7669,10 +7669,10 @@
         </is>
       </c>
       <c r="B232" s="17" t="n">
-        <v>0.2338901506020283</v>
+        <v>0.2880256374470839</v>
       </c>
       <c r="C232" s="17" t="n">
-        <v>0.2094493783303767</v>
+        <v>0.2618117229129708</v>
       </c>
       <c r="D232" s="17" t="n">
         <v>1</v>
@@ -7683,10 +7683,10 @@
         </is>
       </c>
       <c r="H232" s="17" t="n">
-        <v>0.2055301107879665</v>
+        <v>0.2551603020363578</v>
       </c>
       <c r="I232" s="17" t="n">
-        <v>0.184412563008924</v>
+        <v>0.230515703761155</v>
       </c>
       <c r="J232" s="17" t="n">
         <v>1</v>
@@ -7748,10 +7748,10 @@
         <v>1</v>
       </c>
       <c r="C237" s="17" t="n">
-        <v>0.3112074303405577</v>
+        <v>0.3890092879256971</v>
       </c>
       <c r="D237" s="17" t="n">
-        <v>0.799858117029447</v>
+        <v>0.8170590002878688</v>
       </c>
       <c r="G237" s="13" t="inlineStr">
         <is>
@@ -7762,10 +7762,10 @@
         <v>1</v>
       </c>
       <c r="I237" s="17" t="n">
-        <v>0.3058038692461604</v>
+        <v>0.3822548365577004</v>
       </c>
       <c r="J237" s="17" t="n">
-        <v>0.7454265516760136</v>
+        <v>0.7680751028100065</v>
       </c>
     </row>
     <row r="238" ht="18" customHeight="1">
@@ -7775,13 +7775,13 @@
         </is>
       </c>
       <c r="B238" s="17" t="n">
-        <v>0.3112074303405577</v>
+        <v>0.3890092879256971</v>
       </c>
       <c r="C238" s="17" t="n">
         <v>1</v>
       </c>
       <c r="D238" s="17" t="n">
-        <v>0.3317465216323289</v>
+        <v>0.4069611443184033</v>
       </c>
       <c r="G238" s="13" t="inlineStr">
         <is>
@@ -7789,13 +7789,13 @@
         </is>
       </c>
       <c r="H238" s="17" t="n">
-        <v>0.3058038692461604</v>
+        <v>0.3822548365577004</v>
       </c>
       <c r="I238" s="17" t="n">
         <v>1</v>
       </c>
       <c r="J238" s="17" t="n">
-        <v>0.314174726294612</v>
+        <v>0.3892667313396652</v>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
@@ -7805,10 +7805,10 @@
         </is>
       </c>
       <c r="B239" s="17" t="n">
-        <v>0.799858117029447</v>
+        <v>0.8170590002878688</v>
       </c>
       <c r="C239" s="17" t="n">
-        <v>0.3317465216323289</v>
+        <v>0.4069611443184033</v>
       </c>
       <c r="D239" s="17" t="n">
         <v>1</v>
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="H239" s="17" t="n">
-        <v>0.7454265516760136</v>
+        <v>0.7680751028100065</v>
       </c>
       <c r="I239" s="17" t="n">
-        <v>0.314174726294612</v>
+        <v>0.3892667313396652</v>
       </c>
       <c r="J239" s="17" t="n">
         <v>1</v>
@@ -7884,10 +7884,10 @@
         <v>1</v>
       </c>
       <c r="C244" s="17" t="n">
-        <v>0.3050397877984099</v>
+        <v>0.3812997347480124</v>
       </c>
       <c r="D244" s="17" t="n">
-        <v>0.3050397877984099</v>
+        <v>0.3812997347480124</v>
       </c>
       <c r="G244" s="13" t="inlineStr">
         <is>
@@ -7898,10 +7898,10 @@
         <v>1</v>
       </c>
       <c r="I244" s="17" t="n">
-        <v>0.3007751937984507</v>
+        <v>0.3759689922480634</v>
       </c>
       <c r="J244" s="17" t="n">
-        <v>0.3007751937984507</v>
+        <v>0.3759689922480634</v>
       </c>
     </row>
     <row r="245" ht="18" customHeight="1">
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="B245" s="17" t="n">
-        <v>0.3050397877984099</v>
+        <v>0.3812997347480124</v>
       </c>
       <c r="C245" s="17" t="n">
         <v>1</v>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="H245" s="17" t="n">
-        <v>0.3007751937984507</v>
+        <v>0.3759689922480634</v>
       </c>
       <c r="I245" s="17" t="n">
         <v>1</v>
@@ -7941,7 +7941,7 @@
         </is>
       </c>
       <c r="B246" s="17" t="n">
-        <v>0.3050397877984099</v>
+        <v>0.3812997347480124</v>
       </c>
       <c r="C246" s="17" t="n">
         <v>1</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="H246" s="17" t="n">
-        <v>0.3007751937984507</v>
+        <v>0.3759689922480634</v>
       </c>
       <c r="I246" s="17" t="n">
         <v>1</v>
@@ -8020,10 +8020,10 @@
         <v>1</v>
       </c>
       <c r="C251" s="17" t="n">
-        <v>0.3487508050842734</v>
+        <v>0.4359385063553417</v>
       </c>
       <c r="D251" s="17" t="n">
-        <v>0.3487508050842734</v>
+        <v>0.4359385063553417</v>
       </c>
       <c r="G251" s="13" t="inlineStr">
         <is>
@@ -8034,10 +8034,10 @@
         <v>1</v>
       </c>
       <c r="I251" s="17" t="n">
-        <v>0.3355430902600706</v>
+        <v>0.4194288628250882</v>
       </c>
       <c r="J251" s="17" t="n">
-        <v>0.3391953436846079</v>
+        <v>0.4225573979965641</v>
       </c>
     </row>
     <row r="252" ht="18" customHeight="1">
@@ -8047,7 +8047,7 @@
         </is>
       </c>
       <c r="B252" s="17" t="n">
-        <v>0.3487508050842734</v>
+        <v>0.4359385063553417</v>
       </c>
       <c r="C252" s="17" t="n">
         <v>1</v>
@@ -8061,13 +8061,13 @@
         </is>
       </c>
       <c r="H252" s="17" t="n">
-        <v>0.3355430902600706</v>
+        <v>0.4194288628250882</v>
       </c>
       <c r="I252" s="17" t="n">
         <v>1</v>
       </c>
       <c r="J252" s="17" t="n">
-        <v>0.9963087107721955</v>
+        <v>0.9968226700744401</v>
       </c>
     </row>
     <row r="253" ht="18" customHeight="1">
@@ -8077,7 +8077,7 @@
         </is>
       </c>
       <c r="B253" s="17" t="n">
-        <v>0.3487508050842734</v>
+        <v>0.4359385063553417</v>
       </c>
       <c r="C253" s="17" t="n">
         <v>1</v>
@@ -8091,10 +8091,10 @@
         </is>
       </c>
       <c r="H253" s="17" t="n">
-        <v>0.3391953436846079</v>
+        <v>0.4225573979965641</v>
       </c>
       <c r="I253" s="17" t="n">
-        <v>0.9963087107721955</v>
+        <v>0.9968226700744401</v>
       </c>
       <c r="J253" s="17" t="n">
         <v>1</v>
@@ -8156,10 +8156,10 @@
         <v>1</v>
       </c>
       <c r="C258" s="17" t="n">
-        <v>0.3632484261444</v>
+        <v>0.4540605326805</v>
       </c>
       <c r="D258" s="17" t="n">
-        <v>0.3632484261444</v>
+        <v>0.4540605326805</v>
       </c>
       <c r="G258" s="13" t="inlineStr">
         <is>
@@ -8170,10 +8170,10 @@
         <v>1</v>
       </c>
       <c r="I258" s="17" t="n">
-        <v>0.3544561658784907</v>
+        <v>0.4430702073481134</v>
       </c>
       <c r="J258" s="17" t="n">
-        <v>0.3580698814282344</v>
+        <v>0.4461422650800903</v>
       </c>
     </row>
     <row r="259" ht="18" customHeight="1">
@@ -8183,7 +8183,7 @@
         </is>
       </c>
       <c r="B259" s="17" t="n">
-        <v>0.3632484261444</v>
+        <v>0.4540605326805</v>
       </c>
       <c r="C259" s="17" t="n">
         <v>1</v>
@@ -8197,13 +8197,13 @@
         </is>
       </c>
       <c r="H259" s="17" t="n">
-        <v>0.3544561658784907</v>
+        <v>0.4430702073481134</v>
       </c>
       <c r="I259" s="17" t="n">
         <v>1</v>
       </c>
       <c r="J259" s="17" t="n">
-        <v>0.9963676556744399</v>
+        <v>0.9969046562982526</v>
       </c>
     </row>
     <row r="260" ht="18" customHeight="1">
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="B260" s="17" t="n">
-        <v>0.3632484261444</v>
+        <v>0.4540605326805</v>
       </c>
       <c r="C260" s="17" t="n">
         <v>1</v>
@@ -8227,10 +8227,10 @@
         </is>
       </c>
       <c r="H260" s="17" t="n">
-        <v>0.3580698814282344</v>
+        <v>0.4461422650800903</v>
       </c>
       <c r="I260" s="17" t="n">
-        <v>0.9963676556744399</v>
+        <v>0.9969046562982526</v>
       </c>
       <c r="J260" s="17" t="n">
         <v>1</v>
@@ -8292,10 +8292,10 @@
         <v>1</v>
       </c>
       <c r="C265" s="17" t="n">
-        <v>0.1258017250781217</v>
+        <v>0.1572521563476521</v>
       </c>
       <c r="D265" s="17" t="n">
-        <v>0.1258017250781217</v>
+        <v>0.1572521563476521</v>
       </c>
       <c r="G265" s="13" t="inlineStr">
         <is>
@@ -8306,10 +8306,10 @@
         <v>1</v>
       </c>
       <c r="I265" s="17" t="n">
-        <v>0.08319382581527769</v>
+        <v>0.1039922822690971</v>
       </c>
       <c r="J265" s="17" t="n">
-        <v>0.08319382581527769</v>
+        <v>0.1039922822690971</v>
       </c>
     </row>
     <row r="266" ht="18" customHeight="1">
@@ -8319,7 +8319,7 @@
         </is>
       </c>
       <c r="B266" s="17" t="n">
-        <v>0.1258017250781217</v>
+        <v>0.1572521563476521</v>
       </c>
       <c r="C266" s="17" t="n">
         <v>1</v>
@@ -8333,7 +8333,7 @@
         </is>
       </c>
       <c r="H266" s="17" t="n">
-        <v>0.08319382581527769</v>
+        <v>0.1039922822690971</v>
       </c>
       <c r="I266" s="17" t="n">
         <v>1</v>
@@ -8349,7 +8349,7 @@
         </is>
       </c>
       <c r="B267" s="17" t="n">
-        <v>0.1258017250781217</v>
+        <v>0.1572521563476521</v>
       </c>
       <c r="C267" s="17" t="n">
         <v>1</v>
@@ -8363,7 +8363,7 @@
         </is>
       </c>
       <c r="H267" s="17" t="n">
-        <v>0.08319382581527769</v>
+        <v>0.1039922822690971</v>
       </c>
       <c r="I267" s="17" t="n">
         <v>1</v>
@@ -8428,10 +8428,10 @@
         <v>1</v>
       </c>
       <c r="C272" s="17" t="n">
-        <v>0.2959302325581365</v>
+        <v>0.3699127906976706</v>
       </c>
       <c r="D272" s="17" t="n">
-        <v>0.2959302325581365</v>
+        <v>0.3699127906976706</v>
       </c>
       <c r="G272" s="13" t="inlineStr">
         <is>
@@ -8442,10 +8442,10 @@
         <v>1</v>
       </c>
       <c r="I272" s="17" t="n">
-        <v>0.2896119168953493</v>
+        <v>0.3620148961191866</v>
       </c>
       <c r="J272" s="17" t="n">
-        <v>0.2896119168953493</v>
+        <v>0.3620148961191866</v>
       </c>
     </row>
     <row r="273" ht="18" customHeight="1">
@@ -8455,7 +8455,7 @@
         </is>
       </c>
       <c r="B273" s="17" t="n">
-        <v>0.2959302325581365</v>
+        <v>0.3699127906976706</v>
       </c>
       <c r="C273" s="17" t="n">
         <v>1</v>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="H273" s="17" t="n">
-        <v>0.2896119168953493</v>
+        <v>0.3620148961191866</v>
       </c>
       <c r="I273" s="17" t="n">
         <v>1</v>
@@ -8485,7 +8485,7 @@
         </is>
       </c>
       <c r="B274" s="17" t="n">
-        <v>0.2959302325581365</v>
+        <v>0.3699127906976706</v>
       </c>
       <c r="C274" s="17" t="n">
         <v>1</v>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="H274" s="17" t="n">
-        <v>0.2896119168953493</v>
+        <v>0.3620148961191866</v>
       </c>
       <c r="I274" s="17" t="n">
         <v>1</v>
@@ -8556,10 +8556,10 @@
         <v>1</v>
       </c>
       <c r="C280" s="17" t="n">
-        <v>0.184885106366221</v>
+        <v>0.2307915214968191</v>
       </c>
       <c r="D280" s="17" t="n">
-        <v>0.1840521073051553</v>
+        <v>0.2300651341314441</v>
       </c>
     </row>
     <row r="281" ht="18" customHeight="1">
@@ -8569,13 +8569,13 @@
         </is>
       </c>
       <c r="B281" s="17" t="n">
-        <v>0.184885106366221</v>
+        <v>0.2307915214968191</v>
       </c>
       <c r="C281" s="17" t="n">
         <v>1</v>
       </c>
       <c r="D281" s="17" t="n">
-        <v>0.9990403549312348</v>
+        <v>0.9991153051250006</v>
       </c>
     </row>
     <row r="282" ht="18" customHeight="1">
@@ -8585,10 +8585,10 @@
         </is>
       </c>
       <c r="B282" s="17" t="n">
-        <v>0.1840521073051553</v>
+        <v>0.2300651341314441</v>
       </c>
       <c r="C282" s="17" t="n">
-        <v>0.9990403549312348</v>
+        <v>0.9991153051250006</v>
       </c>
       <c r="D282" s="17" t="n">
         <v>1</v>
@@ -8631,10 +8631,10 @@
         <v>1</v>
       </c>
       <c r="C287" s="17" t="n">
-        <v>0.7723203483133553</v>
+        <v>0.7808620366988834</v>
       </c>
       <c r="D287" s="17" t="n">
-        <v>0.240625003658652</v>
+        <v>0.3007812545733151</v>
       </c>
     </row>
     <row r="288" ht="18" customHeight="1">
@@ -8644,13 +8644,13 @@
         </is>
       </c>
       <c r="B288" s="17" t="n">
-        <v>0.7723203483133553</v>
+        <v>0.7808620366988834</v>
       </c>
       <c r="C288" s="17" t="n">
         <v>1</v>
       </c>
       <c r="D288" s="17" t="n">
-        <v>0.2452857786773412</v>
+        <v>0.3028034472700354</v>
       </c>
     </row>
     <row r="289" ht="18" customHeight="1">
@@ -8660,10 +8660,10 @@
         </is>
       </c>
       <c r="B289" s="17" t="n">
-        <v>0.240625003658652</v>
+        <v>0.3007812545733151</v>
       </c>
       <c r="C289" s="17" t="n">
-        <v>0.2452857786773412</v>
+        <v>0.3028034472700354</v>
       </c>
       <c r="D289" s="17" t="n">
         <v>1</v>
@@ -8706,10 +8706,10 @@
         <v>1</v>
       </c>
       <c r="C294" s="17" t="n">
-        <v>0.2069557294542701</v>
+        <v>0.2586946618178376</v>
       </c>
       <c r="D294" s="17" t="n">
-        <v>0.7474043470656565</v>
+        <v>0.7499931338779799</v>
       </c>
     </row>
     <row r="295" ht="18" customHeight="1">
@@ -8719,13 +8719,13 @@
         </is>
       </c>
       <c r="B295" s="17" t="n">
-        <v>0.2069557294542701</v>
+        <v>0.2586946618178376</v>
       </c>
       <c r="C295" s="17" t="n">
         <v>1</v>
       </c>
       <c r="D295" s="17" t="n">
-        <v>0.2080000727533149</v>
+        <v>0.255973785511843</v>
       </c>
     </row>
     <row r="296" ht="18" customHeight="1">
@@ -8735,10 +8735,10 @@
         </is>
       </c>
       <c r="B296" s="17" t="n">
-        <v>0.7474043470656565</v>
+        <v>0.7499931338779799</v>
       </c>
       <c r="C296" s="17" t="n">
-        <v>0.2080000727533149</v>
+        <v>0.255973785511843</v>
       </c>
       <c r="D296" s="17" t="n">
         <v>1</v>
@@ -8781,10 +8781,10 @@
         <v>1</v>
       </c>
       <c r="C301" s="17" t="n">
-        <v>0.8301088880186245</v>
+        <v>0.8349210803297117</v>
       </c>
       <c r="D301" s="17" t="n">
-        <v>0.2197101306949974</v>
+        <v>0.2715929697417209</v>
       </c>
     </row>
     <row r="302" ht="18" customHeight="1">
@@ -8794,13 +8794,13 @@
         </is>
       </c>
       <c r="B302" s="17" t="n">
-        <v>0.8301088880186245</v>
+        <v>0.8349210803297117</v>
       </c>
       <c r="C302" s="17" t="n">
         <v>1</v>
       </c>
       <c r="D302" s="17" t="n">
-        <v>0.1969309706696503</v>
+        <v>0.2461637133370629</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="1">
@@ -8810,10 +8810,10 @@
         </is>
       </c>
       <c r="B303" s="17" t="n">
-        <v>0.2197101306949974</v>
+        <v>0.2715929697417209</v>
       </c>
       <c r="C303" s="17" t="n">
-        <v>0.1969309706696503</v>
+        <v>0.2461637133370629</v>
       </c>
       <c r="D303" s="17" t="n">
         <v>1</v>
@@ -8856,10 +8856,10 @@
         <v>1</v>
       </c>
       <c r="C308" s="17" t="n">
-        <v>0.308505649793359</v>
+        <v>0.3856320622416988</v>
       </c>
       <c r="D308" s="17" t="n">
-        <v>0.7726423343527302</v>
+        <v>0.7925670515489376</v>
       </c>
     </row>
     <row r="309" ht="18" customHeight="1">
@@ -8869,13 +8869,13 @@
         </is>
       </c>
       <c r="B309" s="17" t="n">
-        <v>0.308505649793359</v>
+        <v>0.3856320622416988</v>
       </c>
       <c r="C309" s="17" t="n">
         <v>1</v>
       </c>
       <c r="D309" s="17" t="n">
-        <v>0.3229606239634705</v>
+        <v>0.3981139378290343</v>
       </c>
     </row>
     <row r="310" ht="18" customHeight="1">
@@ -8885,10 +8885,10 @@
         </is>
       </c>
       <c r="B310" s="17" t="n">
-        <v>0.7726423343527302</v>
+        <v>0.7925670515489376</v>
       </c>
       <c r="C310" s="17" t="n">
-        <v>0.3229606239634705</v>
+        <v>0.3981139378290343</v>
       </c>
       <c r="D310" s="17" t="n">
         <v>1</v>
@@ -8931,10 +8931,10 @@
         <v>1</v>
       </c>
       <c r="C315" s="17" t="n">
-        <v>0.3029074907984303</v>
+        <v>0.3786343634980379</v>
       </c>
       <c r="D315" s="17" t="n">
-        <v>0.3029074907984303</v>
+        <v>0.3786343634980379</v>
       </c>
     </row>
     <row r="316" ht="18" customHeight="1">
@@ -8944,7 +8944,7 @@
         </is>
       </c>
       <c r="B316" s="17" t="n">
-        <v>0.3029074907984303</v>
+        <v>0.3786343634980379</v>
       </c>
       <c r="C316" s="17" t="n">
         <v>1</v>
@@ -8960,7 +8960,7 @@
         </is>
       </c>
       <c r="B317" s="17" t="n">
-        <v>0.3029074907984303</v>
+        <v>0.3786343634980379</v>
       </c>
       <c r="C317" s="17" t="n">
         <v>1</v>
@@ -9006,10 +9006,10 @@
         <v>1</v>
       </c>
       <c r="C322" s="17" t="n">
-        <v>0.342146947672172</v>
+        <v>0.4276836845902149</v>
       </c>
       <c r="D322" s="17" t="n">
-        <v>0.3439730743844406</v>
+        <v>0.4292479521759529</v>
       </c>
     </row>
     <row r="323" ht="18" customHeight="1">
@@ -9019,13 +9019,13 @@
         </is>
       </c>
       <c r="B323" s="17" t="n">
-        <v>0.342146947672172</v>
+        <v>0.4276836845902149</v>
       </c>
       <c r="C323" s="17" t="n">
         <v>1</v>
       </c>
       <c r="D323" s="17" t="n">
-        <v>0.9981543553860978</v>
+        <v>0.9984113350372201</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="1">
@@ -9035,10 +9035,10 @@
         </is>
       </c>
       <c r="B324" s="17" t="n">
-        <v>0.3439730743844406</v>
+        <v>0.4292479521759529</v>
       </c>
       <c r="C324" s="17" t="n">
-        <v>0.9981543553860978</v>
+        <v>0.9984113350372201</v>
       </c>
       <c r="D324" s="17" t="n">
         <v>1</v>
@@ -9081,10 +9081,10 @@
         <v>1</v>
       </c>
       <c r="C329" s="17" t="n">
-        <v>0.3588522960114454</v>
+        <v>0.4485653700143066</v>
       </c>
       <c r="D329" s="17" t="n">
-        <v>0.3606591537863172</v>
+        <v>0.4501013988802951</v>
       </c>
     </row>
     <row r="330" ht="18" customHeight="1">
@@ -9094,13 +9094,13 @@
         </is>
       </c>
       <c r="B330" s="17" t="n">
-        <v>0.3588522960114454</v>
+        <v>0.4485653700143066</v>
       </c>
       <c r="C330" s="17" t="n">
         <v>1</v>
       </c>
       <c r="D330" s="17" t="n">
-        <v>0.9981838278372199</v>
+        <v>0.9984523281491263</v>
       </c>
     </row>
     <row r="331" ht="18" customHeight="1">
@@ -9110,10 +9110,10 @@
         </is>
       </c>
       <c r="B331" s="17" t="n">
-        <v>0.3606591537863172</v>
+        <v>0.4501013988802951</v>
       </c>
       <c r="C331" s="17" t="n">
-        <v>0.9981838278372199</v>
+        <v>0.9984523281491263</v>
       </c>
       <c r="D331" s="17" t="n">
         <v>1</v>
@@ -9156,10 +9156,10 @@
         <v>1</v>
       </c>
       <c r="C336" s="17" t="n">
-        <v>0.1044977754466997</v>
+        <v>0.1306222193083746</v>
       </c>
       <c r="D336" s="17" t="n">
-        <v>0.1044977754466997</v>
+        <v>0.1306222193083746</v>
       </c>
     </row>
     <row r="337" ht="18" customHeight="1">
@@ -9169,7 +9169,7 @@
         </is>
       </c>
       <c r="B337" s="17" t="n">
-        <v>0.1044977754466997</v>
+        <v>0.1306222193083746</v>
       </c>
       <c r="C337" s="17" t="n">
         <v>1</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="B338" s="17" t="n">
-        <v>0.1044977754466997</v>
+        <v>0.1306222193083746</v>
       </c>
       <c r="C338" s="17" t="n">
         <v>1</v>
@@ -9231,10 +9231,10 @@
         <v>1</v>
       </c>
       <c r="C343" s="17" t="n">
-        <v>0.2927710747267429</v>
+        <v>0.3659638434084286</v>
       </c>
       <c r="D343" s="17" t="n">
-        <v>0.2927710747267429</v>
+        <v>0.3659638434084286</v>
       </c>
     </row>
     <row r="344" ht="18" customHeight="1">
@@ -9244,7 +9244,7 @@
         </is>
       </c>
       <c r="B344" s="17" t="n">
-        <v>0.2927710747267429</v>
+        <v>0.3659638434084286</v>
       </c>
       <c r="C344" s="17" t="n">
         <v>1</v>
@@ -9260,7 +9260,7 @@
         </is>
       </c>
       <c r="B345" s="17" t="n">
-        <v>0.2927710747267429</v>
+        <v>0.3659638434084286</v>
       </c>
       <c r="C345" s="17" t="n">
         <v>1</v>
@@ -9310,13 +9310,13 @@
         </is>
       </c>
       <c r="B350" s="17" t="n">
-        <v>0.4290863748319284</v>
+        <v>0.4612635101016234</v>
       </c>
       <c r="C350" s="17" t="n">
-        <v>0.7550816738823602</v>
+        <v>0.768883578499046</v>
       </c>
       <c r="D350" s="17" t="n">
-        <v>0.754927738670917</v>
+        <v>0.7687541317769334</v>
       </c>
     </row>
     <row r="351" ht="18" customHeight="1">
@@ -9326,13 +9326,13 @@
         </is>
       </c>
       <c r="B351" s="17" t="n">
-        <v>0.6279461059574674</v>
+        <v>0.6545711128389911</v>
       </c>
       <c r="C351" s="17" t="n">
-        <v>0.6298104159649431</v>
+        <v>0.6553799899176791</v>
       </c>
       <c r="D351" s="17" t="n">
-        <v>0.545773234700798</v>
+        <v>0.5810754105530052</v>
       </c>
     </row>
     <row r="352" ht="18" customHeight="1">
@@ -9342,13 +9342,13 @@
         </is>
       </c>
       <c r="B352" s="17" t="n">
-        <v>0.6610484576625436</v>
+        <v>0.6776056520965432</v>
       </c>
       <c r="C352" s="17" t="n">
-        <v>0.445286747937607</v>
+        <v>0.4799979127500885</v>
       </c>
       <c r="D352" s="17" t="n">
-        <v>0.6866213259456915</v>
+        <v>0.7017900758169469</v>
       </c>
     </row>
     <row r="353" ht="18" customHeight="1">
@@ -9358,13 +9358,13 @@
         </is>
       </c>
       <c r="B353" s="17" t="n">
-        <v>0.6369167186835863</v>
+        <v>0.6591135119956018</v>
       </c>
       <c r="C353" s="17" t="n">
-        <v>0.6278050546734475</v>
+        <v>0.6489418094337386</v>
       </c>
       <c r="D353" s="17" t="n">
-        <v>0.5249923304093943</v>
+        <v>0.5553270049236352</v>
       </c>
     </row>
     <row r="354" ht="18" customHeight="1">
@@ -9374,13 +9374,13 @@
         </is>
       </c>
       <c r="B354" s="17" t="n">
-        <v>0.7016086286790998</v>
+        <v>0.7327164392920847</v>
       </c>
       <c r="C354" s="17" t="n">
-        <v>0.5217359445233959</v>
+        <v>0.5749351938041234</v>
       </c>
       <c r="D354" s="17" t="n">
-        <v>0.7286808874948603</v>
+        <v>0.7572042968133916</v>
       </c>
     </row>
     <row r="355" ht="18" customHeight="1">
@@ -9390,13 +9390,13 @@
         </is>
       </c>
       <c r="B355" s="17" t="n">
-        <v>0.5120352435589012</v>
+        <v>0.5650440544486265</v>
       </c>
       <c r="C355" s="17" t="n">
-        <v>0.7908722472395291</v>
+        <v>0.8135903090494114</v>
       </c>
       <c r="D355" s="17" t="n">
-        <v>0.7908722472395291</v>
+        <v>0.8135903090494114</v>
       </c>
     </row>
     <row r="356" ht="18" customHeight="1">
@@ -9406,13 +9406,13 @@
         </is>
       </c>
       <c r="B356" s="17" t="n">
-        <v>0.5402333140554278</v>
+        <v>0.6000042862474456</v>
       </c>
       <c r="C356" s="17" t="n">
-        <v>0.8019058264560907</v>
+        <v>0.8276696393919525</v>
       </c>
       <c r="D356" s="17" t="n">
-        <v>0.8026382289311615</v>
+        <v>0.828297786163952</v>
       </c>
     </row>
     <row r="357" ht="18" customHeight="1">
@@ -9422,13 +9422,13 @@
         </is>
       </c>
       <c r="B357" s="17" t="n">
-        <v>0.5519193503179605</v>
+        <v>0.61461017055641</v>
       </c>
       <c r="C357" s="17" t="n">
-        <v>0.8069292199383216</v>
+        <v>0.8339505422639425</v>
       </c>
       <c r="D357" s="17" t="n">
-        <v>0.8076528944870611</v>
+        <v>0.8345661181088264</v>
       </c>
     </row>
     <row r="358" ht="18" customHeight="1">
@@ -9438,13 +9438,13 @@
         </is>
       </c>
       <c r="B358" s="17" t="n">
-        <v>0.3731484428126898</v>
+        <v>0.3914355535158622</v>
       </c>
       <c r="C358" s="17" t="n">
-        <v>0.7313493326340099</v>
+        <v>0.7391866657925124</v>
       </c>
       <c r="D358" s="17" t="n">
-        <v>0.7313493326340099</v>
+        <v>0.7391866657925124</v>
       </c>
     </row>
     <row r="359" ht="18" customHeight="1">
@@ -9454,13 +9454,13 @@
         </is>
       </c>
       <c r="B359" s="17" t="n">
-        <v>0.50493975230872</v>
+        <v>0.5561746903859001</v>
       </c>
       <c r="C359" s="17" t="n">
-        <v>0.7878313224180229</v>
+        <v>0.8097891530225285</v>
       </c>
       <c r="D359" s="17" t="n">
-        <v>0.7878313224180229</v>
+        <v>0.8097891530225285</v>
       </c>
     </row>
     <row r="360" ht="18" customHeight="1"/>
@@ -9504,13 +9504,13 @@
         </is>
       </c>
       <c r="B364" s="17" t="n">
-        <v>0.2212816806799083</v>
+        <v>0.2307585314368302</v>
       </c>
       <c r="C364" s="17" t="n">
-        <v>0.3893988521838615</v>
+        <v>0.3846531137510636</v>
       </c>
       <c r="D364" s="17" t="n">
-        <v>0.3893194671362302</v>
+        <v>0.3845883548121061</v>
       </c>
     </row>
     <row r="365" ht="18" customHeight="1">
@@ -9520,13 +9520,13 @@
         </is>
       </c>
       <c r="B365" s="17" t="n">
-        <v>0.3481761826503965</v>
+        <v>0.3461459203410958</v>
       </c>
       <c r="C365" s="17" t="n">
-        <v>0.3492098833701264</v>
+        <v>0.3465736653108225</v>
       </c>
       <c r="D365" s="17" t="n">
-        <v>0.3026139339794771</v>
+        <v>0.3072804143480816</v>
       </c>
     </row>
     <row r="366" ht="18" customHeight="1">
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="B366" s="17" t="n">
-        <v>0.3686918483699124</v>
+        <v>0.3644229157709284</v>
       </c>
       <c r="C366" s="17" t="n">
-        <v>0.2483533427069154</v>
+        <v>0.2581475499608503</v>
       </c>
       <c r="D366" s="17" t="n">
-        <v>0.3829548089231722</v>
+        <v>0.3774295342682213</v>
       </c>
     </row>
     <row r="367" ht="18" customHeight="1">
@@ -9552,13 +9552,13 @@
         </is>
       </c>
       <c r="B367" s="17" t="n">
-        <v>0.3558762359547841</v>
+        <v>0.3537188813449911</v>
       </c>
       <c r="C367" s="17" t="n">
-        <v>0.3507851077176185</v>
+        <v>0.3482601505102025</v>
       </c>
       <c r="D367" s="17" t="n">
-        <v>0.2933386563275975</v>
+        <v>0.2980209681448063</v>
       </c>
     </row>
     <row r="368" ht="18" customHeight="1">
@@ -9568,13 +9568,13 @@
         </is>
       </c>
       <c r="B368" s="17" t="n">
-        <v>0.3594259618050535</v>
+        <v>0.3548511199636884</v>
       </c>
       <c r="C368" s="17" t="n">
-        <v>0.2672792722370573</v>
+        <v>0.2784384060292741</v>
       </c>
       <c r="D368" s="17" t="n">
-        <v>0.3732947659578892</v>
+        <v>0.3667104740070375</v>
       </c>
     </row>
     <row r="369" ht="18" customHeight="1">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="B369" s="17" t="n">
-        <v>0.2445506727649966</v>
+        <v>0.2577491538730032</v>
       </c>
       <c r="C369" s="17" t="n">
-        <v>0.3777246636175017</v>
+        <v>0.3711254230634984</v>
       </c>
       <c r="D369" s="17" t="n">
-        <v>0.3777246636175017</v>
+        <v>0.3711254230634984</v>
       </c>
     </row>
     <row r="370" ht="18" customHeight="1">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="B370" s="17" t="n">
-        <v>0.251883165941744</v>
+        <v>0.265962681672024</v>
       </c>
       <c r="C370" s="17" t="n">
-        <v>0.3738876761201866</v>
+        <v>0.3668794404918936</v>
       </c>
       <c r="D370" s="17" t="n">
-        <v>0.3742291579380693</v>
+        <v>0.3671578778360823</v>
       </c>
     </row>
     <row r="371" ht="18" customHeight="1">
@@ -9616,13 +9616,13 @@
         </is>
       </c>
       <c r="B371" s="17" t="n">
-        <v>0.2547514318820662</v>
+        <v>0.2691966833512609</v>
       </c>
       <c r="C371" s="17" t="n">
-        <v>0.3724572695056614</v>
+        <v>0.3652668485020362</v>
       </c>
       <c r="D371" s="17" t="n">
-        <v>0.3727912986122724</v>
+        <v>0.3655364681467028</v>
       </c>
     </row>
     <row r="372" ht="18" customHeight="1">
@@ -9632,13 +9632,13 @@
         </is>
       </c>
       <c r="B372" s="17" t="n">
-        <v>0.2032568187025109</v>
+        <v>0.2093452205917516</v>
       </c>
       <c r="C372" s="17" t="n">
-        <v>0.3983715906487446</v>
+        <v>0.3953273897041242</v>
       </c>
       <c r="D372" s="17" t="n">
-        <v>0.3983715906487446</v>
+        <v>0.3953273897041242</v>
       </c>
     </row>
     <row r="373" ht="18" customHeight="1">
@@ -9648,13 +9648,13 @@
         </is>
       </c>
       <c r="B373" s="17" t="n">
-        <v>0.2426892101064838</v>
+        <v>0.2556240029535674</v>
       </c>
       <c r="C373" s="17" t="n">
-        <v>0.3786553949467581</v>
+        <v>0.3721879985232163</v>
       </c>
       <c r="D373" s="17" t="n">
-        <v>0.3786553949467581</v>
+        <v>0.3721879985232163</v>
       </c>
     </row>
   </sheetData>
@@ -9894,49 +9894,49 @@
         </is>
       </c>
       <c r="C6" s="17" t="n">
-        <v>11.33</v>
+        <v>11.35</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>20.56</v>
+        <v>20.57</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>23.55</v>
+        <v>23.58</v>
       </c>
       <c r="F6" s="17" t="n">
         <v>24.72</v>
       </c>
       <c r="G6" s="17" t="n">
-        <v>13.44</v>
+        <v>13.46</v>
       </c>
       <c r="H6" s="17" t="n">
-        <v>20.56</v>
+        <v>20.57</v>
       </c>
       <c r="I6" s="17" t="n">
-        <v>23.55</v>
+        <v>23.58</v>
       </c>
       <c r="J6" s="17" t="n">
-        <v>24.33</v>
+        <v>24.34</v>
       </c>
       <c r="K6" s="17" t="n">
-        <v>12.6</v>
+        <v>12.62</v>
       </c>
       <c r="L6" s="17" t="n">
-        <v>20.56</v>
+        <v>20.57</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>23.55</v>
+        <v>23.58</v>
       </c>
       <c r="N6" s="17" t="n">
         <v>24.49</v>
       </c>
       <c r="O6" s="17" t="n">
-        <v>18.97</v>
+        <v>18.98</v>
       </c>
       <c r="P6" s="17" t="n">
-        <v>23.74</v>
+        <v>23.76</v>
       </c>
       <c r="Q6" s="17" t="n">
-        <v>21.35</v>
+        <v>21.37</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -9949,49 +9949,49 @@
         </is>
       </c>
       <c r="C7" s="17" t="n">
-        <v>10.43</v>
+        <v>10.42</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>18.7</v>
+        <v>18.68</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>22.62</v>
+        <v>22.61</v>
       </c>
       <c r="F7" s="17" t="n">
         <v>24.24</v>
       </c>
       <c r="G7" s="17" t="n">
-        <v>12.4</v>
+        <v>12.39</v>
       </c>
       <c r="H7" s="17" t="n">
-        <v>18.7</v>
+        <v>18.68</v>
       </c>
       <c r="I7" s="17" t="n">
-        <v>22.62</v>
+        <v>22.61</v>
       </c>
       <c r="J7" s="17" t="n">
         <v>23.76</v>
       </c>
       <c r="K7" s="17" t="n">
-        <v>11.61</v>
+        <v>11.6</v>
       </c>
       <c r="L7" s="17" t="n">
-        <v>18.7</v>
+        <v>18.68</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>22.62</v>
+        <v>22.61</v>
       </c>
       <c r="N7" s="17" t="n">
         <v>23.95</v>
       </c>
       <c r="O7" s="17" t="n">
-        <v>17.28</v>
+        <v>17.26</v>
       </c>
       <c r="P7" s="17" t="n">
-        <v>22.89</v>
+        <v>22.88</v>
       </c>
       <c r="Q7" s="17" t="n">
-        <v>20.09</v>
+        <v>20.07</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -10007,7 +10007,7 @@
         <v>7.34</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>13.02</v>
+        <v>13.01</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>19.23</v>
@@ -10016,10 +10016,10 @@
         <v>22.66</v>
       </c>
       <c r="G8" s="17" t="n">
-        <v>8.960000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H8" s="17" t="n">
-        <v>13.02</v>
+        <v>13.01</v>
       </c>
       <c r="I8" s="17" t="n">
         <v>19.23</v>
@@ -10031,7 +10031,7 @@
         <v>8.31</v>
       </c>
       <c r="L8" s="17" t="n">
-        <v>13.02</v>
+        <v>13.01</v>
       </c>
       <c r="M8" s="17" t="n">
         <v>19.23</v>
@@ -10040,7 +10040,7 @@
         <v>22.08</v>
       </c>
       <c r="O8" s="17" t="n">
-        <v>12.08</v>
+        <v>12.07</v>
       </c>
       <c r="P8" s="17" t="n">
         <v>19.8</v>
@@ -10059,49 +10059,49 @@
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>5.32</v>
+        <v>5.31</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>11.64</v>
+        <v>11.62</v>
       </c>
       <c r="E9" s="17" t="n">
         <v>16.64</v>
       </c>
       <c r="F9" s="17" t="n">
-        <v>19.23</v>
+        <v>19.21</v>
       </c>
       <c r="G9" s="17" t="n">
-        <v>6.65</v>
+        <v>6.64</v>
       </c>
       <c r="H9" s="17" t="n">
-        <v>11.64</v>
+        <v>11.62</v>
       </c>
       <c r="I9" s="17" t="n">
         <v>16.64</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>18.49</v>
+        <v>18.47</v>
       </c>
       <c r="K9" s="17" t="n">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="L9" s="17" t="n">
-        <v>11.64</v>
+        <v>11.62</v>
       </c>
       <c r="M9" s="17" t="n">
         <v>16.64</v>
       </c>
       <c r="N9" s="17" t="n">
-        <v>18.79</v>
+        <v>18.77</v>
       </c>
       <c r="O9" s="17" t="n">
-        <v>10.54</v>
+        <v>10.52</v>
       </c>
       <c r="P9" s="17" t="n">
         <v>17.07</v>
       </c>
       <c r="Q9" s="17" t="n">
-        <v>13.8</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -10117,10 +10117,10 @@
         <v>6.71</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>12.27</v>
+        <v>12.26</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>15.65</v>
+        <v>15.68</v>
       </c>
       <c r="F10" s="17" t="n">
         <v>18.55</v>
@@ -10129,10 +10129,10 @@
         <v>8.01</v>
       </c>
       <c r="H10" s="17" t="n">
-        <v>12.27</v>
+        <v>12.26</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>15.65</v>
+        <v>15.68</v>
       </c>
       <c r="J10" s="17" t="n">
         <v>17.67</v>
@@ -10141,10 +10141,10 @@
         <v>7.49</v>
       </c>
       <c r="L10" s="17" t="n">
-        <v>12.27</v>
+        <v>12.26</v>
       </c>
       <c r="M10" s="17" t="n">
-        <v>15.65</v>
+        <v>15.68</v>
       </c>
       <c r="N10" s="17" t="n">
         <v>18.02</v>
@@ -10153,10 +10153,10 @@
         <v>11.31</v>
       </c>
       <c r="P10" s="17" t="n">
-        <v>16.12</v>
+        <v>16.15</v>
       </c>
       <c r="Q10" s="17" t="n">
-        <v>13.71</v>
+        <v>13.73</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -10169,49 +10169,49 @@
         </is>
       </c>
       <c r="C11" s="17" t="n">
-        <v>5.27</v>
+        <v>5.29</v>
       </c>
       <c r="D11" s="17" t="n">
-        <v>10.51</v>
+        <v>10.52</v>
       </c>
       <c r="E11" s="17" t="n">
-        <v>16.86</v>
+        <v>16.87</v>
       </c>
       <c r="F11" s="17" t="n">
-        <v>20.27</v>
+        <v>20.3</v>
       </c>
       <c r="G11" s="17" t="n">
-        <v>6.61</v>
+        <v>6.64</v>
       </c>
       <c r="H11" s="17" t="n">
-        <v>10.51</v>
+        <v>10.52</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>16.86</v>
+        <v>16.87</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>19.32</v>
+        <v>19.35</v>
       </c>
       <c r="K11" s="17" t="n">
-        <v>6.07</v>
+        <v>6.1</v>
       </c>
       <c r="L11" s="17" t="n">
-        <v>10.51</v>
+        <v>10.52</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>16.86</v>
+        <v>16.87</v>
       </c>
       <c r="N11" s="17" t="n">
-        <v>19.7</v>
+        <v>19.73</v>
       </c>
       <c r="O11" s="17" t="n">
-        <v>9.619999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="P11" s="17" t="n">
-        <v>17.43</v>
+        <v>17.44</v>
       </c>
       <c r="Q11" s="17" t="n">
-        <v>13.52</v>
+        <v>13.54</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -10224,10 +10224,10 @@
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>4.87</v>
+        <v>4.86</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>8.9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="E12" s="17" t="n">
         <v>12.68</v>
@@ -10239,19 +10239,19 @@
         <v>5.97</v>
       </c>
       <c r="H12" s="17" t="n">
-        <v>8.9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="I12" s="17" t="n">
         <v>12.68</v>
       </c>
       <c r="J12" s="17" t="n">
-        <v>15.66</v>
+        <v>15.67</v>
       </c>
       <c r="K12" s="17" t="n">
         <v>5.53</v>
       </c>
       <c r="L12" s="17" t="n">
-        <v>8.9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M12" s="17" t="n">
         <v>12.68</v>
@@ -10260,7 +10260,7 @@
         <v>16.18</v>
       </c>
       <c r="O12" s="17" t="n">
-        <v>8.23</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="P12" s="17" t="n">
         <v>13.38</v>
@@ -10279,49 +10279,49 @@
         </is>
       </c>
       <c r="C13" s="17" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="D13" s="17" t="n">
-        <v>5.79</v>
+        <v>5.78</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>11.88</v>
+        <v>11.87</v>
       </c>
       <c r="F13" s="17" t="n">
-        <v>15.41</v>
+        <v>15.4</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H13" s="17" t="n">
-        <v>5.79</v>
+        <v>5.78</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>11.88</v>
+        <v>11.87</v>
       </c>
       <c r="J13" s="17" t="n">
-        <v>14.4</v>
+        <v>14.38</v>
       </c>
       <c r="K13" s="17" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="L13" s="17" t="n">
-        <v>5.79</v>
+        <v>5.78</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>11.88</v>
+        <v>11.87</v>
       </c>
       <c r="N13" s="17" t="n">
-        <v>14.8</v>
+        <v>14.79</v>
       </c>
       <c r="O13" s="17" t="n">
-        <v>4.94</v>
+        <v>4.93</v>
       </c>
       <c r="P13" s="17" t="n">
-        <v>12.46</v>
+        <v>12.45</v>
       </c>
       <c r="Q13" s="17" t="n">
-        <v>8.699999999999999</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -10337,22 +10337,22 @@
         <v>2.43</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>4.73</v>
+        <v>4.74</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>6.99</v>
+        <v>7.01</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>11.8</v>
+        <v>11.82</v>
       </c>
       <c r="G14" s="17" t="n">
         <v>3.01</v>
       </c>
       <c r="H14" s="17" t="n">
-        <v>4.73</v>
+        <v>4.74</v>
       </c>
       <c r="I14" s="17" t="n">
-        <v>6.99</v>
+        <v>7.01</v>
       </c>
       <c r="J14" s="17" t="n">
         <v>10.32</v>
@@ -10361,22 +10361,22 @@
         <v>2.78</v>
       </c>
       <c r="L14" s="17" t="n">
-        <v>4.73</v>
+        <v>4.74</v>
       </c>
       <c r="M14" s="17" t="n">
-        <v>6.99</v>
+        <v>7.01</v>
       </c>
       <c r="N14" s="17" t="n">
-        <v>10.91</v>
+        <v>10.92</v>
       </c>
       <c r="O14" s="17" t="n">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="P14" s="17" t="n">
-        <v>7.77</v>
+        <v>7.79</v>
       </c>
       <c r="Q14" s="17" t="n">
-        <v>6.05</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -10392,46 +10392,46 @@
         <v>0</v>
       </c>
       <c r="D15" s="17" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="E15" s="17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="F15" s="17" t="n">
-        <v>7.28</v>
+        <v>7.25</v>
       </c>
       <c r="G15" s="17" t="n">
         <v>0.06</v>
       </c>
       <c r="H15" s="17" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J15" s="17" t="n">
-        <v>5.63</v>
+        <v>5.64</v>
       </c>
       <c r="K15" s="17" t="n">
         <v>0.04</v>
       </c>
       <c r="L15" s="17" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="M15" s="17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="N15" s="17" t="n">
-        <v>6.29</v>
+        <v>6.28</v>
       </c>
       <c r="O15" s="17" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="P15" s="17" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="Q15" s="17" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1"/>
@@ -10478,10 +10478,10 @@
         </is>
       </c>
       <c r="C19" s="17" t="n">
-        <v>21.35</v>
+        <v>21.37</v>
       </c>
       <c r="D19" s="17" t="n">
-        <v>21.35</v>
+        <v>21.37</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>20.09</v>
+        <v>20.07</v>
       </c>
       <c r="D20" s="17" t="n">
-        <v>21.35</v>
+        <v>21.37</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -10526,7 +10526,7 @@
         </is>
       </c>
       <c r="C22" s="17" t="n">
-        <v>13.8</v>
+        <v>13.79</v>
       </c>
       <c r="D22" s="17" t="n">
         <v>15.94</v>
@@ -10542,7 +10542,7 @@
         </is>
       </c>
       <c r="C23" s="17" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="D23" s="17" t="n">
         <v>15.94</v>
@@ -10558,10 +10558,10 @@
         </is>
       </c>
       <c r="C24" s="17" t="n">
-        <v>13.71</v>
+        <v>13.73</v>
       </c>
       <c r="D24" s="17" t="n">
-        <v>13.71</v>
+        <v>13.73</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -10574,10 +10574,10 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>13.52</v>
+        <v>13.54</v>
       </c>
       <c r="D25" s="17" t="n">
-        <v>13.52</v>
+        <v>13.54</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -10606,7 +10606,7 @@
         </is>
       </c>
       <c r="C27" s="17" t="n">
-        <v>8.699999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="D27" s="17" t="n">
         <v>10.8</v>
@@ -10622,10 +10622,10 @@
         </is>
       </c>
       <c r="C28" s="17" t="n">
-        <v>6.05</v>
+        <v>6.07</v>
       </c>
       <c r="D28" s="17" t="n">
-        <v>6.05</v>
+        <v>6.07</v>
       </c>
     </row>
   </sheetData>
